--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +39,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -74,14 +81,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -656,6 +666,583 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D5AFE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Likes, commentaires, partages, enregistrements</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF4F81"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$F$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8E5CFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$G$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$H$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$I$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Taux d'engagement</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E5133A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$K$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues cumulées de chaque vidéo, jour après jour</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues gagnées chaque jour, vidéo par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -741,6 +1328,131 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1165,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1259,8 +1971,58 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:17</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Des millions publics promis. 244 salariés de </t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
+        <v/>
+      </c>
+      <c r="L2" s="6">
+        <f>IFERROR(D2/E2,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1270,10 +2032,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1282,6 +2045,11 @@
           <t>Jour</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Des millions publics promis.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1289,9 +2057,13 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1301,11 +2073,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1316,6 +2089,11 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Des millions publics promis.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -1327,12 +2105,17 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>SUM(B2:A2)</f>
+        <f>IF('Évolution par vidéo'!B2="","",'Évolution par vidéo'!B2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="3">
+        <f>SUM(B2:B2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1421,56 +2204,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Décodé · suivi du compte Décodé - l'éco simplement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Mis à jour automatiquement par l'agent 3 à chaque relevé (9 h et 16 h, heure de Paris).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Source : API Instagram (insights). Les vues et partages sont cumulés depuis la publication.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>« Abonnés gagnés » et « Vues du jour » = différence avec le relevé de la veille (formules).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>« Vues du jour par vidéo » = vues gagnées par chaque vidéo depuis le relevé de la veille.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>« Heure par heure » : relevé toutes les heures de 7 h à 23 h (Paris) ; le relevé de 7 h inclut la nuit.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Les statistiques d'une story ne sont lisibles que pendant ses 24 h : dernier relevé conservé.</t>
         </is>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -11,8 +11,10 @@
     <sheet name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="À lire" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Heure par heure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vues gagnées par heure" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stories" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="À lire" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -268,6 +270,422 @@
             </rich>
           </tx>
         </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues cumulées de chaque vidéo, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues totales du compte (vidéos), heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues gagnées chaque heure, vidéo par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1444,6 +1862,104 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2125,6 +2641,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Abonnés</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>10-25 Des millions publics p</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Vues totales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:00</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3">
+        <f>SUM(C2:C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3">
+        <f>SUM(C3:C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:00</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3">
+        <f>SUM(C4:C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:00</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3">
+        <f>SUM(C5:C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 15:00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3">
+        <f>SUM(C6:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3">
+        <f>SUM(C7:C7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>10-25 Des millions publics p</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total de l'heure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <f>'Heure par heure'!A2</f>
+        <v/>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3">
+        <f>SUM(B2:B2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <f>'Heure par heure'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="3">
+        <f>IF('Heure par heure'!C3="","",'Heure par heure'!C3-N('Heure par heure'!C2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>SUM(B3:B3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <f>'Heure par heure'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Heure par heure'!C4="","",'Heure par heure'!C4-N('Heure par heure'!C3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>SUM(B4:B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <f>'Heure par heure'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Heure par heure'!C5="","",'Heure par heure'!C5-N('Heure par heure'!C4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>SUM(B5:B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <f>'Heure par heure'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Heure par heure'!C6="","",'Heure par heure'!C6-N('Heure par heure'!C5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>SUM(B6:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <f>'Heure par heure'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Heure par heure'!C7="","",'Heure par heure'!C7-N('Heure par heure'!C6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>SUM(B7:B7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2191,7 +2960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$7</f>
+              <f>'Heure par heure'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$7</f>
+              <f>'Heure par heure'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$7</f>
+              <f>'Heure par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$7</f>
+              <f>'Heure par heure'!$D$2:$D$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$7</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$7</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2761,6 +2761,23 @@
       </c>
       <c r="D7" s="3">
         <f>SUM(C7:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 17:00</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="D8" s="3">
+        <f>SUM(C8:C8)</f>
         <v/>
       </c>
     </row>
@@ -2776,7 +2793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2879,6 +2896,20 @@
       </c>
       <c r="C7" s="3">
         <f>SUM(B7:B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <f>'Heure par heure'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Heure par heure'!C8="","",'Heure par heure'!C8-N('Heure par heure'!C7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>SUM(B8:B8)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$8</f>
+              <f>'Heure par heure'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$8</f>
+              <f>'Heure par heure'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$8</f>
+              <f>'Heure par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$8</f>
+              <f>'Heure par heure'!$D$2:$D$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$8</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$8</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2778,6 +2778,23 @@
       </c>
       <c r="D8" s="3">
         <f>SUM(C8:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 18:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D9" s="3">
+        <f>SUM(C9:C9)</f>
         <v/>
       </c>
     </row>
@@ -2793,7 +2810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2910,6 +2927,20 @@
       </c>
       <c r="C8" s="3">
         <f>SUM(B8:B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <f>'Heure par heure'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="3">
+        <f>IF('Heure par heure'!C9="","",'Heure par heure'!C9-N('Heure par heure'!C8))</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>SUM(B9:B9)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$9</f>
+              <f>'Heure par heure'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$9</f>
+              <f>'Heure par heure'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$9</f>
+              <f>'Heure par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$9</f>
+              <f>'Heure par heure'!$D$2:$D$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$9</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$9</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2795,6 +2795,23 @@
       </c>
       <c r="D9" s="3">
         <f>SUM(C9:C9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 19:00</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D10" s="3">
+        <f>SUM(C10:C10)</f>
         <v/>
       </c>
     </row>
@@ -2810,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2941,6 +2958,20 @@
       </c>
       <c r="C9" s="3">
         <f>SUM(B9:B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <f>'Heure par heure'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="3">
+        <f>IF('Heure par heure'!C10="","",'Heure par heure'!C10-N('Heure par heure'!C9))</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>SUM(B10:B10)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$10</f>
+              <f>'Heure par heure'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$10</f>
+              <f>'Heure par heure'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$10</f>
+              <f>'Heure par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$10</f>
+              <f>'Heure par heure'!$D$2:$D$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$10</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$10</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2812,6 +2812,23 @@
       </c>
       <c r="D10" s="3">
         <f>SUM(C10:C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D11" s="3">
+        <f>SUM(C11:C11)</f>
         <v/>
       </c>
     </row>
@@ -2827,7 +2844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2972,6 +2989,20 @@
       </c>
       <c r="C10" s="3">
         <f>SUM(B10:B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <f>'Heure par heure'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="3">
+        <f>IF('Heure par heure'!C11="","",'Heure par heure'!C11-N('Heure par heure'!C10))</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>SUM(B11:B11)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$11</f>
+              <f>'Heure par heure'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$11</f>
+              <f>'Heure par heure'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$11</f>
+              <f>'Heure par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$11</f>
+              <f>'Heure par heure'!$D$2:$D$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$11</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$11</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2829,23 @@
       </c>
       <c r="D11" s="3">
         <f>SUM(C11:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:00</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D12" s="3">
+        <f>SUM(C12:C12)</f>
         <v/>
       </c>
     </row>
@@ -2844,7 +2861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3003,6 +3020,20 @@
       </c>
       <c r="C11" s="3">
         <f>SUM(B11:B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <f>'Heure par heure'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="3">
+        <f>IF('Heure par heure'!C12="","",'Heure par heure'!C12-N('Heure par heure'!C11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>SUM(B12:B12)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$12</f>
+              <f>'Heure par heure'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$12</f>
+              <f>'Heure par heure'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$12</f>
+              <f>'Heure par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$12</f>
+              <f>'Heure par heure'!$D$2:$D$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$12</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$12</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2846,6 +2846,23 @@
       </c>
       <c r="D12" s="3">
         <f>SUM(C12:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 22:00</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D13" s="3">
+        <f>SUM(C13:C13)</f>
         <v/>
       </c>
     </row>
@@ -2861,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3034,6 +3051,20 @@
       </c>
       <c r="C12" s="3">
         <f>SUM(B12:B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <f>'Heure par heure'!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="3">
+        <f>IF('Heure par heure'!C13="","",'Heure par heure'!C13-N('Heure par heure'!C12))</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>SUM(B13:B13)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$13</f>
+              <f>'Heure par heure'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$13</f>
+              <f>'Heure par heure'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$13</f>
+              <f>'Heure par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$13</f>
+              <f>'Heure par heure'!$D$2:$D$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$13</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$13</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2863,6 +2863,23 @@
       </c>
       <c r="D13" s="3">
         <f>SUM(C13:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:00</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D14" s="3">
+        <f>SUM(C14:C14)</f>
         <v/>
       </c>
     </row>
@@ -2878,7 +2895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3065,6 +3082,20 @@
       </c>
       <c r="C13" s="3">
         <f>SUM(B13:B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <f>'Heure par heure'!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="3">
+        <f>IF('Heure par heure'!C14="","",'Heure par heure'!C14-N('Heure par heure'!C13))</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>SUM(B14:B14)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$14</f>
+              <f>'Heure par heure'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$14</f>
+              <f>'Heure par heure'!$B$2:$B$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$14</f>
+              <f>'Heure par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$14</f>
+              <f>'Heure par heure'!$D$2:$D$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$14</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$14</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2880,6 +2880,23 @@
       </c>
       <c r="D14" s="3">
         <f>SUM(C14:C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(C15:C15)</f>
         <v/>
       </c>
     </row>
@@ -2895,7 +2912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3096,6 +3113,20 @@
       </c>
       <c r="C14" s="3">
         <f>SUM(B14:B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <f>'Heure par heure'!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="3">
+        <f>IF('Heure par heure'!C15="","",'Heure par heure'!C15-N('Heure par heure'!C14))</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>SUM(B15:B15)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$15</f>
+              <f>'Heure par heure'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$15</f>
+              <f>'Heure par heure'!$B$2:$B$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$15</f>
+              <f>'Heure par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$15</f>
+              <f>'Heure par heure'!$D$2:$D$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$15</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$15</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2641,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2897,6 +2897,23 @@
       </c>
       <c r="D15" s="3">
         <f>SUM(C15:C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:00</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D16" s="3">
+        <f>SUM(C16:C16)</f>
         <v/>
       </c>
     </row>
@@ -2912,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3127,6 +3144,20 @@
       </c>
       <c r="C15" s="3">
         <f>SUM(B15:B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <f>'Heure par heure'!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="3">
+        <f>IF('Heure par heure'!C16="","",'Heure par heure'!C16-N('Heure par heure'!C15))</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>SUM(B16:B16)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2</f>
+              <f>'Jour par jour'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2</f>
+              <f>'Jour par jour'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -767,12 +767,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2</f>
+              <f>'Jour par jour'!$L$2:$L$3</f>
             </numRef>
           </val>
         </ser>
@@ -880,12 +880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2</f>
+              <f>'Jour par jour'!$F$2:$F$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -920,12 +920,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2</f>
+              <f>'Jour par jour'!$H$2:$H$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1022,12 +1022,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2</f>
+              <f>'Jour par jour'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1515,12 +1515,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2</f>
+              <f>'Évolution par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2</f>
+              <f>'Évolution par vidéo'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1613,12 +1613,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1831,7 +1831,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1858,7 +1858,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2266,7 +2266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2394,6 +2394,51 @@
       </c>
       <c r="M2" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <f>IF(ROW()=2,"",B3-B2)</f>
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="E3" s="3">
+        <f>IF(ROW()=2,D3,D3-D2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2504,13 +2549,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -2522,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -2548,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2575,6 +2620,16 @@
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2589,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2626,6 +2681,21 @@
       </c>
       <c r="C2" s="3">
         <f>SUM(B2:B2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>IF('Évolution par vidéo'!B3="","",'Évolution par vidéo'!B3-N('Évolution par vidéo'!B2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>SUM(B3:B3)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$16</f>
+              <f>'Heure par heure'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$16</f>
+              <f>'Heure par heure'!$B$2:$B$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$16</f>
+              <f>'Heure par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$16</f>
+              <f>'Heure par heure'!$D$2:$D$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$16</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$16</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2984,6 +2984,23 @@
       </c>
       <c r="D16" s="3">
         <f>SUM(C16:C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D17" s="3">
+        <f>SUM(C17:C17)</f>
         <v/>
       </c>
     </row>
@@ -2999,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3228,6 +3245,20 @@
       </c>
       <c r="C16" s="3">
         <f>SUM(B16:B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <f>'Heure par heure'!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="3">
+        <f>IF('Heure par heure'!C17="","",'Heure par heure'!C17-N('Heure par heure'!C16))</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>SUM(B17:B17)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$17</f>
+              <f>'Heure par heure'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$17</f>
+              <f>'Heure par heure'!$B$2:$B$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$17</f>
+              <f>'Heure par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$17</f>
+              <f>'Heure par heure'!$D$2:$D$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$17</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$17</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3001,23 @@
       </c>
       <c r="D17" s="3">
         <f>SUM(C17:C17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D18" s="3">
+        <f>SUM(C18:C18)</f>
         <v/>
       </c>
     </row>
@@ -3016,7 +3033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3259,6 +3276,20 @@
       </c>
       <c r="C17" s="3">
         <f>SUM(B17:B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <f>'Heure par heure'!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="3">
+        <f>IF('Heure par heure'!C18="","",'Heure par heure'!C18-N('Heure par heure'!C17))</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>SUM(B18:B18)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$18</f>
+              <f>'Heure par heure'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$18</f>
+              <f>'Heure par heure'!$B$2:$B$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$18</f>
+              <f>'Heure par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$18</f>
+              <f>'Heure par heure'!$D$2:$D$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$18</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$18</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3018,6 +3018,23 @@
       </c>
       <c r="D18" s="3">
         <f>SUM(C18:C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3">
+        <f>SUM(C19:C19)</f>
         <v/>
       </c>
     </row>
@@ -3033,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3290,6 +3307,20 @@
       </c>
       <c r="C18" s="3">
         <f>SUM(B18:B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <f>'Heure par heure'!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="3">
+        <f>IF('Heure par heure'!C19="","",'Heure par heure'!C19-N('Heure par heure'!C18))</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(B19:B19)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$19</f>
+              <f>'Heure par heure'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$19</f>
+              <f>'Heure par heure'!$B$2:$B$20</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$19</f>
+              <f>'Heure par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$19</f>
+              <f>'Heure par heure'!$D$2:$D$20</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$19</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$19</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3035,6 +3035,23 @@
       </c>
       <c r="D19" s="3">
         <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D20" s="3">
+        <f>SUM(C20:C20)</f>
         <v/>
       </c>
     </row>
@@ -3050,7 +3067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3321,6 +3338,20 @@
       </c>
       <c r="C19" s="3">
         <f>SUM(B19:B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <f>'Heure par heure'!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="3">
+        <f>IF('Heure par heure'!C20="","",'Heure par heure'!C20-N('Heure par heure'!C19))</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>SUM(B20:B20)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$20</f>
+              <f>'Heure par heure'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$20</f>
+              <f>'Heure par heure'!$B$2:$B$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$20</f>
+              <f>'Heure par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$20</f>
+              <f>'Heure par heure'!$D$2:$D$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$20</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$20</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3052,6 +3052,23 @@
       </c>
       <c r="D20" s="3">
         <f>SUM(C20:C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D21" s="3">
+        <f>SUM(C21:C21)</f>
         <v/>
       </c>
     </row>
@@ -3067,7 +3084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3352,6 +3369,20 @@
       </c>
       <c r="C20" s="3">
         <f>SUM(B20:B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <f>'Heure par heure'!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="3">
+        <f>IF('Heure par heure'!C21="","",'Heure par heure'!C21-N('Heure par heure'!C20))</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>SUM(B21:B21)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$21</f>
+              <f>'Heure par heure'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$21</f>
+              <f>'Heure par heure'!$B$2:$B$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$21</f>
+              <f>'Heure par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$21</f>
+              <f>'Heure par heure'!$D$2:$D$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$21</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$21</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3069,6 +3069,23 @@
       </c>
       <c r="D21" s="3">
         <f>SUM(C21:C21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D22" s="3">
+        <f>SUM(C22:C22)</f>
         <v/>
       </c>
     </row>
@@ -3084,7 +3101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3383,6 +3400,20 @@
       </c>
       <c r="C21" s="3">
         <f>SUM(B21:B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <f>'Heure par heure'!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="3">
+        <f>IF('Heure par heure'!C22="","",'Heure par heure'!C22-N('Heure par heure'!C21))</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>SUM(B22:B22)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -2410,17 +2410,17 @@
         <v/>
       </c>
       <c r="D3" s="3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E3" s="3">
         <f>IF(ROW()=2,D3,D3-D2)</f>
         <v/>
       </c>
       <c r="F3" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$22</f>
+              <f>'Heure par heure'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$22</f>
+              <f>'Heure par heure'!$B$2:$B$23</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$22</f>
+              <f>'Heure par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$22</f>
+              <f>'Heure par heure'!$D$2:$D$23</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$22</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$22</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3086,6 +3086,23 @@
       </c>
       <c r="D22" s="3">
         <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D23" s="3">
+        <f>SUM(C23:C23)</f>
         <v/>
       </c>
     </row>
@@ -3101,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3431,20 @@
       </c>
       <c r="C22" s="3">
         <f>SUM(B22:B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <f>'Heure par heure'!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="3">
+        <f>IF('Heure par heure'!C23="","",'Heure par heure'!C23-N('Heure par heure'!C22))</f>
+        <v/>
+      </c>
+      <c r="C23" s="3">
+        <f>SUM(B23:B23)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$23</f>
+              <f>'Heure par heure'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$23</f>
+              <f>'Heure par heure'!$B$2:$B$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$23</f>
+              <f>'Heure par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$23</f>
+              <f>'Heure par heure'!$D$2:$D$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$23</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$23</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3103,6 +3103,23 @@
       </c>
       <c r="D23" s="3">
         <f>SUM(C23:C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:00</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D24" s="3">
+        <f>SUM(C24:C24)</f>
         <v/>
       </c>
     </row>
@@ -3118,7 +3135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3445,6 +3462,20 @@
       </c>
       <c r="C23" s="3">
         <f>SUM(B23:B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <f>'Heure par heure'!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="3">
+        <f>IF('Heure par heure'!C24="","",'Heure par heure'!C24-N('Heure par heure'!C23))</f>
+        <v/>
+      </c>
+      <c r="C24" s="3">
+        <f>SUM(B24:B24)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$24</f>
+              <f>'Heure par heure'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$24</f>
+              <f>'Heure par heure'!$B$2:$B$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$24</f>
+              <f>'Heure par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$24</f>
+              <f>'Heure par heure'!$D$2:$D$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$24</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$24</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3120,6 +3120,23 @@
       </c>
       <c r="D24" s="3">
         <f>SUM(C24:C24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D25" s="3">
+        <f>SUM(C25:C25)</f>
         <v/>
       </c>
     </row>
@@ -3135,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3476,6 +3493,20 @@
       </c>
       <c r="C24" s="3">
         <f>SUM(B24:B24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <f>'Heure par heure'!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="3">
+        <f>IF('Heure par heure'!C25="","",'Heure par heure'!C25-N('Heure par heure'!C24))</f>
+        <v/>
+      </c>
+      <c r="C25" s="3">
+        <f>SUM(B25:B25)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$25</f>
+              <f>'Heure par heure'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$25</f>
+              <f>'Heure par heure'!$B$2:$B$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$25</f>
+              <f>'Heure par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$25</f>
+              <f>'Heure par heure'!$D$2:$D$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$25</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$25</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3137,6 +3137,23 @@
       </c>
       <c r="D25" s="3">
         <f>SUM(C25:C25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 20:00</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D26" s="3">
+        <f>SUM(C26:C26)</f>
         <v/>
       </c>
     </row>
@@ -3152,7 +3169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3507,6 +3524,20 @@
       </c>
       <c r="C25" s="3">
         <f>SUM(B25:B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <f>'Heure par heure'!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="3">
+        <f>IF('Heure par heure'!C26="","",'Heure par heure'!C26-N('Heure par heure'!C25))</f>
+        <v/>
+      </c>
+      <c r="C26" s="3">
+        <f>SUM(B26:B26)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$26</f>
+              <f>'Heure par heure'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$26</f>
+              <f>'Heure par heure'!$B$2:$B$27</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$26</f>
+              <f>'Heure par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$26</f>
+              <f>'Heure par heure'!$D$2:$D$27</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$26</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$26</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1885,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +1907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +1929,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +1956,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3154,6 +3154,23 @@
       </c>
       <c r="D26" s="3">
         <f>SUM(C26:C26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D27" s="3">
+        <f>SUM(C27:C27)</f>
         <v/>
       </c>
     </row>
@@ -3169,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3538,6 +3555,20 @@
       </c>
       <c r="C26" s="3">
         <f>SUM(B26:B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <f>'Heure par heure'!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="3">
+        <f>IF('Heure par heure'!C27="","",'Heure par heure'!C27-N('Heure par heure'!C26))</f>
+        <v/>
+      </c>
+      <c r="C27" s="3">
+        <f>SUM(B27:B27)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,76 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$27</f>
+              <f>'Heure par heure'!$C$2:$C$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$D$2:$D$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$E$2:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$27</f>
+              <f>'Heure par heure'!$B$2:$B$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -528,7 +592,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Heure par heure'!D1</f>
+              <f>'Heure par heure'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -553,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$27</f>
+              <f>'Heure par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$27</f>
+              <f>'Heure par heure'!$F$2:$F$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +716,60 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$27</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$27</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$C$2:$C$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -1885,7 +1997,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1907,7 +2019,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1929,7 +2041,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1956,7 +2068,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2711,13 +2823,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2738,6 +2852,16 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>10-27 À qui la France doit-e</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>10-27 Ton salaire brut n'est</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Vues totales</t>
         </is>
       </c>
@@ -2752,8 +2876,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3">
-        <f>SUM(C2:C2)</f>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3">
+        <f>SUM(C2:E2)</f>
         <v/>
       </c>
     </row>
@@ -2767,8 +2893,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3">
-        <f>SUM(C3:C3)</f>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3">
+        <f>SUM(C3:E3)</f>
         <v/>
       </c>
     </row>
@@ -2782,8 +2910,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3">
-        <f>SUM(C4:C4)</f>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3">
+        <f>SUM(C4:E4)</f>
         <v/>
       </c>
     </row>
@@ -2797,8 +2927,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3">
-        <f>SUM(C5:C5)</f>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3">
+        <f>SUM(C5:E5)</f>
         <v/>
       </c>
     </row>
@@ -2812,8 +2944,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3">
-        <f>SUM(C6:C6)</f>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3">
+        <f>SUM(C6:E6)</f>
         <v/>
       </c>
     </row>
@@ -2829,8 +2963,10 @@
       <c r="C7" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="D7" s="3">
-        <f>SUM(C7:C7)</f>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3">
+        <f>SUM(C7:E7)</f>
         <v/>
       </c>
     </row>
@@ -2846,8 +2982,10 @@
       <c r="C8" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="D8" s="3">
-        <f>SUM(C8:C8)</f>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3">
+        <f>SUM(C8:E8)</f>
         <v/>
       </c>
     </row>
@@ -2863,8 +3001,10 @@
       <c r="C9" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="D9" s="3">
-        <f>SUM(C9:C9)</f>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3">
+        <f>SUM(C9:E9)</f>
         <v/>
       </c>
     </row>
@@ -2880,8 +3020,10 @@
       <c r="C10" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="D10" s="3">
-        <f>SUM(C10:C10)</f>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3">
+        <f>SUM(C10:E10)</f>
         <v/>
       </c>
     </row>
@@ -2897,8 +3039,10 @@
       <c r="C11" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D11" s="3">
-        <f>SUM(C11:C11)</f>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3">
+        <f>SUM(C11:E11)</f>
         <v/>
       </c>
     </row>
@@ -2914,8 +3058,10 @@
       <c r="C12" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D12" s="3">
-        <f>SUM(C12:C12)</f>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3">
+        <f>SUM(C12:E12)</f>
         <v/>
       </c>
     </row>
@@ -2931,8 +3077,10 @@
       <c r="C13" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D13" s="3">
-        <f>SUM(C13:C13)</f>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3">
+        <f>SUM(C13:E13)</f>
         <v/>
       </c>
     </row>
@@ -2948,8 +3096,10 @@
       <c r="C14" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D14" s="3">
-        <f>SUM(C14:C14)</f>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3">
+        <f>SUM(C14:E14)</f>
         <v/>
       </c>
     </row>
@@ -2965,8 +3115,10 @@
       <c r="C15" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D15" s="3">
-        <f>SUM(C15:C15)</f>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3">
+        <f>SUM(C15:E15)</f>
         <v/>
       </c>
     </row>
@@ -2982,8 +3134,10 @@
       <c r="C16" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="D16" s="3">
-        <f>SUM(C16:C16)</f>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3">
+        <f>SUM(C16:E16)</f>
         <v/>
       </c>
     </row>
@@ -2999,8 +3153,10 @@
       <c r="C17" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D17" s="3">
-        <f>SUM(C17:C17)</f>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
+        <f>SUM(C17:E17)</f>
         <v/>
       </c>
     </row>
@@ -3016,8 +3172,10 @@
       <c r="C18" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D18" s="3">
-        <f>SUM(C18:C18)</f>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3">
+        <f>SUM(C18:E18)</f>
         <v/>
       </c>
     </row>
@@ -3033,8 +3191,10 @@
       <c r="C19" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D19" s="3">
-        <f>SUM(C19:C19)</f>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3">
+        <f>SUM(C19:E19)</f>
         <v/>
       </c>
     </row>
@@ -3050,8 +3210,10 @@
       <c r="C20" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D20" s="3">
-        <f>SUM(C20:C20)</f>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3">
+        <f>SUM(C20:E20)</f>
         <v/>
       </c>
     </row>
@@ -3067,8 +3229,10 @@
       <c r="C21" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D21" s="3">
-        <f>SUM(C21:C21)</f>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3">
+        <f>SUM(C21:E21)</f>
         <v/>
       </c>
     </row>
@@ -3084,8 +3248,10 @@
       <c r="C22" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D22" s="3">
-        <f>SUM(C22:C22)</f>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3">
+        <f>SUM(C22:E22)</f>
         <v/>
       </c>
     </row>
@@ -3101,8 +3267,10 @@
       <c r="C23" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D23" s="3">
-        <f>SUM(C23:C23)</f>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3">
+        <f>SUM(C23:E23)</f>
         <v/>
       </c>
     </row>
@@ -3118,8 +3286,10 @@
       <c r="C24" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D24" s="3">
-        <f>SUM(C24:C24)</f>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3">
+        <f>SUM(C24:E24)</f>
         <v/>
       </c>
     </row>
@@ -3135,8 +3305,10 @@
       <c r="C25" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D25" s="3">
-        <f>SUM(C25:C25)</f>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3">
+        <f>SUM(C25:E25)</f>
         <v/>
       </c>
     </row>
@@ -3152,8 +3324,10 @@
       <c r="C26" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D26" s="3">
-        <f>SUM(C26:C26)</f>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3">
+        <f>SUM(C26:E26)</f>
         <v/>
       </c>
     </row>
@@ -3169,8 +3343,33 @@
       <c r="C27" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="D27" s="3">
-        <f>SUM(C27:C27)</f>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3">
+        <f>SUM(C27:E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:00</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <f>SUM(C28:E28)</f>
         <v/>
       </c>
     </row>
@@ -3186,12 +3385,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3207,6 +3408,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>10-27 À qui la France doit-e</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>10-27 Ton salaire brut n'est</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total de l'heure</t>
         </is>
       </c>
@@ -3217,8 +3428,10 @@
         <v/>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3">
-        <f>SUM(B2:B2)</f>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3">
+        <f>SUM(B2:D2)</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3445,15 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>SUM(B3:B3)</f>
+        <f>IF('Heure par heure'!D3="","",'Heure par heure'!D3-N('Heure par heure'!D2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>IF('Heure par heure'!E3="","",'Heure par heure'!E3-N('Heure par heure'!E2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(B3:D3)</f>
         <v/>
       </c>
     </row>
@@ -3246,7 +3467,15 @@
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUM(B4:B4)</f>
+        <f>IF('Heure par heure'!D4="","",'Heure par heure'!D4-N('Heure par heure'!D3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>IF('Heure par heure'!E4="","",'Heure par heure'!E4-N('Heure par heure'!E3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(B4:D4)</f>
         <v/>
       </c>
     </row>
@@ -3260,7 +3489,15 @@
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUM(B5:B5)</f>
+        <f>IF('Heure par heure'!D5="","",'Heure par heure'!D5-N('Heure par heure'!D4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>IF('Heure par heure'!E5="","",'Heure par heure'!E5-N('Heure par heure'!E4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(B5:D5)</f>
         <v/>
       </c>
     </row>
@@ -3274,7 +3511,15 @@
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUM(B6:B6)</f>
+        <f>IF('Heure par heure'!D6="","",'Heure par heure'!D6-N('Heure par heure'!D5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>IF('Heure par heure'!E6="","",'Heure par heure'!E6-N('Heure par heure'!E5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>
@@ -3288,7 +3533,15 @@
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>SUM(B7:B7)</f>
+        <f>IF('Heure par heure'!D7="","",'Heure par heure'!D7-N('Heure par heure'!D6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>IF('Heure par heure'!E7="","",'Heure par heure'!E7-N('Heure par heure'!E6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>SUM(B7:D7)</f>
         <v/>
       </c>
     </row>
@@ -3302,7 +3555,15 @@
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>SUM(B8:B8)</f>
+        <f>IF('Heure par heure'!D8="","",'Heure par heure'!D8-N('Heure par heure'!D7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF('Heure par heure'!E8="","",'Heure par heure'!E8-N('Heure par heure'!E7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(B8:D8)</f>
         <v/>
       </c>
     </row>
@@ -3316,7 +3577,15 @@
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>SUM(B9:B9)</f>
+        <f>IF('Heure par heure'!D9="","",'Heure par heure'!D9-N('Heure par heure'!D8))</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF('Heure par heure'!E9="","",'Heure par heure'!E9-N('Heure par heure'!E8))</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM(B9:D9)</f>
         <v/>
       </c>
     </row>
@@ -3330,7 +3599,15 @@
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>SUM(B10:B10)</f>
+        <f>IF('Heure par heure'!D10="","",'Heure par heure'!D10-N('Heure par heure'!D9))</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF('Heure par heure'!E10="","",'Heure par heure'!E10-N('Heure par heure'!E9))</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>SUM(B10:D10)</f>
         <v/>
       </c>
     </row>
@@ -3344,7 +3621,15 @@
         <v/>
       </c>
       <c r="C11" s="3">
-        <f>SUM(B11:B11)</f>
+        <f>IF('Heure par heure'!D11="","",'Heure par heure'!D11-N('Heure par heure'!D10))</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF('Heure par heure'!E11="","",'Heure par heure'!E11-N('Heure par heure'!E10))</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>SUM(B11:D11)</f>
         <v/>
       </c>
     </row>
@@ -3358,7 +3643,15 @@
         <v/>
       </c>
       <c r="C12" s="3">
-        <f>SUM(B12:B12)</f>
+        <f>IF('Heure par heure'!D12="","",'Heure par heure'!D12-N('Heure par heure'!D11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF('Heure par heure'!E12="","",'Heure par heure'!E12-N('Heure par heure'!E11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="3">
+        <f>SUM(B12:D12)</f>
         <v/>
       </c>
     </row>
@@ -3372,7 +3665,15 @@
         <v/>
       </c>
       <c r="C13" s="3">
-        <f>SUM(B13:B13)</f>
+        <f>IF('Heure par heure'!D13="","",'Heure par heure'!D13-N('Heure par heure'!D12))</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF('Heure par heure'!E13="","",'Heure par heure'!E13-N('Heure par heure'!E12))</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>SUM(B13:D13)</f>
         <v/>
       </c>
     </row>
@@ -3386,7 +3687,15 @@
         <v/>
       </c>
       <c r="C14" s="3">
-        <f>SUM(B14:B14)</f>
+        <f>IF('Heure par heure'!D14="","",'Heure par heure'!D14-N('Heure par heure'!D13))</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF('Heure par heure'!E14="","",'Heure par heure'!E14-N('Heure par heure'!E13))</f>
+        <v/>
+      </c>
+      <c r="E14" s="3">
+        <f>SUM(B14:D14)</f>
         <v/>
       </c>
     </row>
@@ -3400,7 +3709,15 @@
         <v/>
       </c>
       <c r="C15" s="3">
-        <f>SUM(B15:B15)</f>
+        <f>IF('Heure par heure'!D15="","",'Heure par heure'!D15-N('Heure par heure'!D14))</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF('Heure par heure'!E15="","",'Heure par heure'!E15-N('Heure par heure'!E14))</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>SUM(B15:D15)</f>
         <v/>
       </c>
     </row>
@@ -3414,7 +3731,15 @@
         <v/>
       </c>
       <c r="C16" s="3">
-        <f>SUM(B16:B16)</f>
+        <f>IF('Heure par heure'!D16="","",'Heure par heure'!D16-N('Heure par heure'!D15))</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF('Heure par heure'!E16="","",'Heure par heure'!E16-N('Heure par heure'!E15))</f>
+        <v/>
+      </c>
+      <c r="E16" s="3">
+        <f>SUM(B16:D16)</f>
         <v/>
       </c>
     </row>
@@ -3428,7 +3753,15 @@
         <v/>
       </c>
       <c r="C17" s="3">
-        <f>SUM(B17:B17)</f>
+        <f>IF('Heure par heure'!D17="","",'Heure par heure'!D17-N('Heure par heure'!D16))</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF('Heure par heure'!E17="","",'Heure par heure'!E17-N('Heure par heure'!E16))</f>
+        <v/>
+      </c>
+      <c r="E17" s="3">
+        <f>SUM(B17:D17)</f>
         <v/>
       </c>
     </row>
@@ -3442,7 +3775,15 @@
         <v/>
       </c>
       <c r="C18" s="3">
-        <f>SUM(B18:B18)</f>
+        <f>IF('Heure par heure'!D18="","",'Heure par heure'!D18-N('Heure par heure'!D17))</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF('Heure par heure'!E18="","",'Heure par heure'!E18-N('Heure par heure'!E17))</f>
+        <v/>
+      </c>
+      <c r="E18" s="3">
+        <f>SUM(B18:D18)</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3797,15 @@
         <v/>
       </c>
       <c r="C19" s="3">
-        <f>SUM(B19:B19)</f>
+        <f>IF('Heure par heure'!D19="","",'Heure par heure'!D19-N('Heure par heure'!D18))</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF('Heure par heure'!E19="","",'Heure par heure'!E19-N('Heure par heure'!E18))</f>
+        <v/>
+      </c>
+      <c r="E19" s="3">
+        <f>SUM(B19:D19)</f>
         <v/>
       </c>
     </row>
@@ -3470,7 +3819,15 @@
         <v/>
       </c>
       <c r="C20" s="3">
-        <f>SUM(B20:B20)</f>
+        <f>IF('Heure par heure'!D20="","",'Heure par heure'!D20-N('Heure par heure'!D19))</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF('Heure par heure'!E20="","",'Heure par heure'!E20-N('Heure par heure'!E19))</f>
+        <v/>
+      </c>
+      <c r="E20" s="3">
+        <f>SUM(B20:D20)</f>
         <v/>
       </c>
     </row>
@@ -3484,7 +3841,15 @@
         <v/>
       </c>
       <c r="C21" s="3">
-        <f>SUM(B21:B21)</f>
+        <f>IF('Heure par heure'!D21="","",'Heure par heure'!D21-N('Heure par heure'!D20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF('Heure par heure'!E21="","",'Heure par heure'!E21-N('Heure par heure'!E20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUM(B21:D21)</f>
         <v/>
       </c>
     </row>
@@ -3498,7 +3863,15 @@
         <v/>
       </c>
       <c r="C22" s="3">
-        <f>SUM(B22:B22)</f>
+        <f>IF('Heure par heure'!D22="","",'Heure par heure'!D22-N('Heure par heure'!D21))</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF('Heure par heure'!E22="","",'Heure par heure'!E22-N('Heure par heure'!E21))</f>
+        <v/>
+      </c>
+      <c r="E22" s="3">
+        <f>SUM(B22:D22)</f>
         <v/>
       </c>
     </row>
@@ -3512,7 +3885,15 @@
         <v/>
       </c>
       <c r="C23" s="3">
-        <f>SUM(B23:B23)</f>
+        <f>IF('Heure par heure'!D23="","",'Heure par heure'!D23-N('Heure par heure'!D22))</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>IF('Heure par heure'!E23="","",'Heure par heure'!E23-N('Heure par heure'!E22))</f>
+        <v/>
+      </c>
+      <c r="E23" s="3">
+        <f>SUM(B23:D23)</f>
         <v/>
       </c>
     </row>
@@ -3526,7 +3907,15 @@
         <v/>
       </c>
       <c r="C24" s="3">
-        <f>SUM(B24:B24)</f>
+        <f>IF('Heure par heure'!D24="","",'Heure par heure'!D24-N('Heure par heure'!D23))</f>
+        <v/>
+      </c>
+      <c r="D24" s="3">
+        <f>IF('Heure par heure'!E24="","",'Heure par heure'!E24-N('Heure par heure'!E23))</f>
+        <v/>
+      </c>
+      <c r="E24" s="3">
+        <f>SUM(B24:D24)</f>
         <v/>
       </c>
     </row>
@@ -3540,7 +3929,15 @@
         <v/>
       </c>
       <c r="C25" s="3">
-        <f>SUM(B25:B25)</f>
+        <f>IF('Heure par heure'!D25="","",'Heure par heure'!D25-N('Heure par heure'!D24))</f>
+        <v/>
+      </c>
+      <c r="D25" s="3">
+        <f>IF('Heure par heure'!E25="","",'Heure par heure'!E25-N('Heure par heure'!E24))</f>
+        <v/>
+      </c>
+      <c r="E25" s="3">
+        <f>SUM(B25:D25)</f>
         <v/>
       </c>
     </row>
@@ -3554,7 +3951,15 @@
         <v/>
       </c>
       <c r="C26" s="3">
-        <f>SUM(B26:B26)</f>
+        <f>IF('Heure par heure'!D26="","",'Heure par heure'!D26-N('Heure par heure'!D25))</f>
+        <v/>
+      </c>
+      <c r="D26" s="3">
+        <f>IF('Heure par heure'!E26="","",'Heure par heure'!E26-N('Heure par heure'!E25))</f>
+        <v/>
+      </c>
+      <c r="E26" s="3">
+        <f>SUM(B26:D26)</f>
         <v/>
       </c>
     </row>
@@ -3568,7 +3973,37 @@
         <v/>
       </c>
       <c r="C27" s="3">
-        <f>SUM(B27:B27)</f>
+        <f>IF('Heure par heure'!D27="","",'Heure par heure'!D27-N('Heure par heure'!D26))</f>
+        <v/>
+      </c>
+      <c r="D27" s="3">
+        <f>IF('Heure par heure'!E27="","",'Heure par heure'!E27-N('Heure par heure'!E26))</f>
+        <v/>
+      </c>
+      <c r="E27" s="3">
+        <f>SUM(B27:D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <f>'Heure par heure'!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="3">
+        <f>IF('Heure par heure'!C28="","",'Heure par heure'!C28-N('Heure par heure'!C27))</f>
+        <v/>
+      </c>
+      <c r="C28" s="3">
+        <f>IF('Heure par heure'!D28="","",'Heure par heure'!D28-N('Heure par heure'!D27))</f>
+        <v/>
+      </c>
+      <c r="D28" s="3">
+        <f>IF('Heure par heure'!E28="","",'Heure par heure'!E28-N('Heure par heure'!E27))</f>
+        <v/>
+      </c>
+      <c r="E28" s="3">
+        <f>SUM(B28:D28)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$3</f>
+              <f>'Jour par jour'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -812,6 +812,108 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues des stories</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Stories'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Stories'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Stories'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -852,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$3</f>
+              <f>'Jour par jour'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -879,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$3</f>
+              <f>'Jour par jour'!$L$2:$L$4</f>
             </numRef>
           </val>
         </ser>
@@ -992,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$3</f>
+              <f>'Jour par jour'!$F$2:$F$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1032,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$3</f>
+              <f>'Jour par jour'!$H$2:$H$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$3</f>
+              <f>'Jour par jour'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1236,12 +1338,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2</f>
+              <f>'Vidéos'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1338,12 +1440,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2</f>
+              <f>'Vidéos'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1365,12 +1467,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2</f>
+              <f>'Vidéos'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1392,12 +1494,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2</f>
+              <f>'Vidéos'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1419,12 +1521,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2</f>
+              <f>'Vidéos'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1521,12 +1623,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2</f>
+              <f>'Vidéos'!$K$2:$K$4</f>
             </numRef>
           </val>
         </ser>
@@ -1627,12 +1729,76 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$3</f>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$3</f>
+              <f>'Évolution par vidéo'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$C$2:$C$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1725,12 +1891,60 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$3</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$3</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$C$2:$C$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1872,7 +2086,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1894,7 +2108,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1916,7 +2130,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1943,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1970,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2072,6 +2286,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2378,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2553,6 +2794,51 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <f>IF(ROW()=2,"",B4-B3)</f>
+        <v/>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="E4" s="3">
+        <f>IF(ROW()=2,D4,D4-D3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2565,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2690,12 +2976,106 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:10</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>À qui la France doit-elle 2 882 milliards d'e</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
+        <v/>
+      </c>
+      <c r="L3" s="6">
+        <f>IFERROR(D3/E3,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:11</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ton salaire brut n'est jamais ton salaire net</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>IFERROR(D4/E4,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2705,11 +3085,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2723,6 +3105,16 @@
           <t>Des millions publics promis.</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À qui la France doit-elle 2 </t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ton salaire brut n'est jamai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2733,6 +3125,8 @@
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2742,6 +3136,24 @@
       </c>
       <c r="B3" s="3" t="n">
         <v>131</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2756,12 +3168,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2777,6 +3191,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">À qui la France doit-elle 2 </t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ton salaire brut n'est jamai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -2792,7 +3216,15 @@
         <v/>
       </c>
       <c r="C2" s="3">
-        <f>SUM(B2:B2)</f>
+        <f>IF('Évolution par vidéo'!C2="","",'Évolution par vidéo'!C2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="3">
+        <f>IF('Évolution par vidéo'!D2="","",'Évolution par vidéo'!D2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>SUM(B2:D2)</f>
         <v/>
       </c>
     </row>
@@ -2807,7 +3239,38 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>SUM(B3:B3)</f>
+        <f>IF('Évolution par vidéo'!C3="","",'Évolution par vidéo'!C3-N('Évolution par vidéo'!C2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>IF('Évolution par vidéo'!D3="","",'Évolution par vidéo'!D3-N('Évolution par vidéo'!D2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(B3:D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Évolution par vidéo'!B4="","",'Évolution par vidéo'!B4-N('Évolution par vidéo'!B3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>IF('Évolution par vidéo'!C4="","",'Évolution par vidéo'!C4-N('Évolution par vidéo'!C3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>IF('Évolution par vidéo'!D4="","",'Évolution par vidéo'!D4-N('Évolution par vidéo'!D3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(B4:D4)</f>
         <v/>
       </c>
     </row>
@@ -4019,7 +4482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4080,8 +4543,113 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:10</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:12</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:15</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$28</f>
+              <f>'Heure par heure'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$28</f>
+              <f>'Heure par heure'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$28</f>
+              <f>'Heure par heure'!$E$2:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$28</f>
+              <f>'Heure par heure'!$B$2:$B$29</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$28</f>
+              <f>'Heure par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$28</f>
+              <f>'Heure par heure'!$F$2:$F$29</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$28</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$28</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$28</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$28</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3836,6 +3836,29 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <f>SUM(C29:E29)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3848,7 +3871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4467,6 +4490,28 @@
       </c>
       <c r="E28" s="3">
         <f>SUM(B28:D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <f>'Heure par heure'!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="3">
+        <f>IF('Heure par heure'!C29="","",'Heure par heure'!C29-N('Heure par heure'!C28))</f>
+        <v/>
+      </c>
+      <c r="C29" s="3">
+        <f>IF('Heure par heure'!D29="","",'Heure par heure'!D29-N('Heure par heure'!D28))</f>
+        <v/>
+      </c>
+      <c r="D29" s="3">
+        <f>IF('Heure par heure'!E29="","",'Heure par heure'!E29-N('Heure par heure'!E28))</f>
+        <v/>
+      </c>
+      <c r="E29" s="3">
+        <f>SUM(B29:D29)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$29</f>
+              <f>'Heure par heure'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$29</f>
+              <f>'Heure par heure'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$29</f>
+              <f>'Heure par heure'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$29</f>
+              <f>'Heure par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$29</f>
+              <f>'Heure par heure'!$F$2:$F$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$29</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$29</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3859,6 +3859,29 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:00</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F30" s="3">
+        <f>SUM(C30:E30)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3871,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4512,6 +4535,28 @@
       </c>
       <c r="E29" s="3">
         <f>SUM(B29:D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <f>'Heure par heure'!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="3">
+        <f>IF('Heure par heure'!C30="","",'Heure par heure'!C30-N('Heure par heure'!C29))</f>
+        <v/>
+      </c>
+      <c r="C30" s="3">
+        <f>IF('Heure par heure'!D30="","",'Heure par heure'!D30-N('Heure par heure'!D29))</f>
+        <v/>
+      </c>
+      <c r="D30" s="3">
+        <f>IF('Heure par heure'!E30="","",'Heure par heure'!E30-N('Heure par heure'!E29))</f>
+        <v/>
+      </c>
+      <c r="E30" s="3">
+        <f>SUM(B30:D30)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$30</f>
+              <f>'Heure par heure'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$30</f>
+              <f>'Heure par heure'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$30</f>
+              <f>'Heure par heure'!$E$2:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$30</f>
+              <f>'Heure par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$30</f>
+              <f>'Heure par heure'!$F$2:$F$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$30</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$30</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3882,6 +3882,29 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:00</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F31" s="3">
+        <f>SUM(C31:E31)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3894,7 +3917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4557,6 +4580,28 @@
       </c>
       <c r="E30" s="3">
         <f>SUM(B30:D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <f>'Heure par heure'!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="3">
+        <f>IF('Heure par heure'!C31="","",'Heure par heure'!C31-N('Heure par heure'!C30))</f>
+        <v/>
+      </c>
+      <c r="C31" s="3">
+        <f>IF('Heure par heure'!D31="","",'Heure par heure'!D31-N('Heure par heure'!D30))</f>
+        <v/>
+      </c>
+      <c r="D31" s="3">
+        <f>IF('Heure par heure'!E31="","",'Heure par heure'!E31-N('Heure par heure'!E30))</f>
+        <v/>
+      </c>
+      <c r="E31" s="3">
+        <f>SUM(B31:D31)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$31</f>
+              <f>'Heure par heure'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$31</f>
+              <f>'Heure par heure'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$31</f>
+              <f>'Heure par heure'!$E$2:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$31</f>
+              <f>'Heure par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$31</f>
+              <f>'Heure par heure'!$F$2:$F$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$31</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$31</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3905,6 +3905,29 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:00</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F32" s="3">
+        <f>SUM(C32:E32)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3917,7 +3940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4602,6 +4625,28 @@
       </c>
       <c r="E31" s="3">
         <f>SUM(B31:D31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f>'Heure par heure'!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="3">
+        <f>IF('Heure par heure'!C32="","",'Heure par heure'!C32-N('Heure par heure'!C31))</f>
+        <v/>
+      </c>
+      <c r="C32" s="3">
+        <f>IF('Heure par heure'!D32="","",'Heure par heure'!D32-N('Heure par heure'!D31))</f>
+        <v/>
+      </c>
+      <c r="D32" s="3">
+        <f>IF('Heure par heure'!E32="","",'Heure par heure'!E32-N('Heure par heure'!E31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="3">
+        <f>SUM(B32:D32)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$32</f>
+              <f>'Heure par heure'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$32</f>
+              <f>'Heure par heure'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$32</f>
+              <f>'Heure par heure'!$E$2:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$32</f>
+              <f>'Heure par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$32</f>
+              <f>'Heure par heure'!$F$2:$F$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$32</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$32</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3928,6 +3928,29 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:00</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F33" s="3">
+        <f>SUM(C33:E33)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3940,7 +3963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4647,6 +4670,28 @@
       </c>
       <c r="E32" s="3">
         <f>SUM(B32:D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <f>'Heure par heure'!A33</f>
+        <v/>
+      </c>
+      <c r="B33" s="3">
+        <f>IF('Heure par heure'!C33="","",'Heure par heure'!C33-N('Heure par heure'!C32))</f>
+        <v/>
+      </c>
+      <c r="C33" s="3">
+        <f>IF('Heure par heure'!D33="","",'Heure par heure'!D33-N('Heure par heure'!D32))</f>
+        <v/>
+      </c>
+      <c r="D33" s="3">
+        <f>IF('Heure par heure'!E33="","",'Heure par heure'!E33-N('Heure par heure'!E32))</f>
+        <v/>
+      </c>
+      <c r="E33" s="3">
+        <f>SUM(B33:D33)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$33</f>
+              <f>'Heure par heure'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$33</f>
+              <f>'Heure par heure'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$33</f>
+              <f>'Heure par heure'!$E$2:$E$34</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$33</f>
+              <f>'Heure par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$33</f>
+              <f>'Heure par heure'!$F$2:$F$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$33</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$33</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3951,6 +3951,29 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="F34" s="3">
+        <f>SUM(C34:E34)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3963,7 +3986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4692,6 +4715,28 @@
       </c>
       <c r="E33" s="3">
         <f>SUM(B33:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <f>'Heure par heure'!A34</f>
+        <v/>
+      </c>
+      <c r="B34" s="3">
+        <f>IF('Heure par heure'!C34="","",'Heure par heure'!C34-N('Heure par heure'!C33))</f>
+        <v/>
+      </c>
+      <c r="C34" s="3">
+        <f>IF('Heure par heure'!D34="","",'Heure par heure'!D34-N('Heure par heure'!D33))</f>
+        <v/>
+      </c>
+      <c r="D34" s="3">
+        <f>IF('Heure par heure'!E34="","",'Heure par heure'!E34-N('Heure par heure'!E33))</f>
+        <v/>
+      </c>
+      <c r="E34" s="3">
+        <f>SUM(B34:D34)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$34</f>
+              <f>'Heure par heure'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$34</f>
+              <f>'Heure par heure'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$34</f>
+              <f>'Heure par heure'!$E$2:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$34</f>
+              <f>'Heure par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$34</f>
+              <f>'Heure par heure'!$F$2:$F$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$34</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$34</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3974,6 +3974,29 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F35" s="3">
+        <f>SUM(C35:E35)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3986,7 +4009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4737,6 +4760,28 @@
       </c>
       <c r="E34" s="3">
         <f>SUM(B34:D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <f>'Heure par heure'!A35</f>
+        <v/>
+      </c>
+      <c r="B35" s="3">
+        <f>IF('Heure par heure'!C35="","",'Heure par heure'!C35-N('Heure par heure'!C34))</f>
+        <v/>
+      </c>
+      <c r="C35" s="3">
+        <f>IF('Heure par heure'!D35="","",'Heure par heure'!D35-N('Heure par heure'!D34))</f>
+        <v/>
+      </c>
+      <c r="D35" s="3">
+        <f>IF('Heure par heure'!E35="","",'Heure par heure'!E35-N('Heure par heure'!E34))</f>
+        <v/>
+      </c>
+      <c r="E35" s="3">
+        <f>SUM(B35:D35)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -2808,26 +2808,26 @@
         <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v>177</v>
+        <v>401</v>
       </c>
       <c r="E4" s="3">
         <f>IF(ROW()=2,D4,D4-D3)</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -3054,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
@@ -3150,10 +3150,10 @@
         <v>131</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$35</f>
+              <f>'Heure par heure'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$35</f>
+              <f>'Heure par heure'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$35</f>
+              <f>'Heure par heure'!$E$2:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$35</f>
+              <f>'Heure par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$35</f>
+              <f>'Heure par heure'!$F$2:$F$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$35</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$35</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3997,6 +3997,29 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:00</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="F36" s="3">
+        <f>SUM(C36:E36)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4009,7 +4032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4782,6 +4805,28 @@
       </c>
       <c r="E35" s="3">
         <f>SUM(B35:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <f>'Heure par heure'!A36</f>
+        <v/>
+      </c>
+      <c r="B36" s="3">
+        <f>IF('Heure par heure'!C36="","",'Heure par heure'!C36-N('Heure par heure'!C35))</f>
+        <v/>
+      </c>
+      <c r="C36" s="3">
+        <f>IF('Heure par heure'!D36="","",'Heure par heure'!D36-N('Heure par heure'!D35))</f>
+        <v/>
+      </c>
+      <c r="D36" s="3">
+        <f>IF('Heure par heure'!E36="","",'Heure par heure'!E36-N('Heure par heure'!E35))</f>
+        <v/>
+      </c>
+      <c r="E36" s="3">
+        <f>SUM(B36:D36)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$36</f>
+              <f>'Heure par heure'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$36</f>
+              <f>'Heure par heure'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$36</f>
+              <f>'Heure par heure'!$E$2:$E$37</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$36</f>
+              <f>'Heure par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$36</f>
+              <f>'Heure par heure'!$F$2:$F$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$36</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$36</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4020,6 +4020,29 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:00</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F37" s="3">
+        <f>SUM(C37:E37)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4032,7 +4055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4827,6 +4850,28 @@
       </c>
       <c r="E36" s="3">
         <f>SUM(B36:D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <f>'Heure par heure'!A37</f>
+        <v/>
+      </c>
+      <c r="B37" s="3">
+        <f>IF('Heure par heure'!C37="","",'Heure par heure'!C37-N('Heure par heure'!C36))</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>IF('Heure par heure'!D37="","",'Heure par heure'!D37-N('Heure par heure'!D36))</f>
+        <v/>
+      </c>
+      <c r="D37" s="3">
+        <f>IF('Heure par heure'!E37="","",'Heure par heure'!E37-N('Heure par heure'!E36))</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>SUM(B37:D37)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$37</f>
+              <f>'Heure par heure'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$37</f>
+              <f>'Heure par heure'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$37</f>
+              <f>'Heure par heure'!$E$2:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$37</f>
+              <f>'Heure par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$37</f>
+              <f>'Heure par heure'!$F$2:$F$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$37</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$37</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4043,6 +4043,29 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:00</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F38" s="3">
+        <f>SUM(C38:E38)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4055,7 +4078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4872,6 +4895,28 @@
       </c>
       <c r="E37" s="3">
         <f>SUM(B37:D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <f>'Heure par heure'!A38</f>
+        <v/>
+      </c>
+      <c r="B38" s="3">
+        <f>IF('Heure par heure'!C38="","",'Heure par heure'!C38-N('Heure par heure'!C37))</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>IF('Heure par heure'!D38="","",'Heure par heure'!D38-N('Heure par heure'!D37))</f>
+        <v/>
+      </c>
+      <c r="D38" s="3">
+        <f>IF('Heure par heure'!E38="","",'Heure par heure'!E38-N('Heure par heure'!E37))</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>SUM(B38:D38)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$38</f>
+              <f>'Heure par heure'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$38</f>
+              <f>'Heure par heure'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$38</f>
+              <f>'Heure par heure'!$E$2:$E$39</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$38</f>
+              <f>'Heure par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$38</f>
+              <f>'Heure par heure'!$F$2:$F$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$38</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$38</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4066,6 +4066,29 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:00</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F39" s="3">
+        <f>SUM(C39:E39)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4078,7 +4101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4917,6 +4940,28 @@
       </c>
       <c r="E38" s="3">
         <f>SUM(B38:D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <f>'Heure par heure'!A39</f>
+        <v/>
+      </c>
+      <c r="B39" s="3">
+        <f>IF('Heure par heure'!C39="","",'Heure par heure'!C39-N('Heure par heure'!C38))</f>
+        <v/>
+      </c>
+      <c r="C39" s="3">
+        <f>IF('Heure par heure'!D39="","",'Heure par heure'!D39-N('Heure par heure'!D38))</f>
+        <v/>
+      </c>
+      <c r="D39" s="3">
+        <f>IF('Heure par heure'!E39="","",'Heure par heure'!E39-N('Heure par heure'!E38))</f>
+        <v/>
+      </c>
+      <c r="E39" s="3">
+        <f>SUM(B39:D39)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$39</f>
+              <f>'Heure par heure'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$39</f>
+              <f>'Heure par heure'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$39</f>
+              <f>'Heure par heure'!$E$2:$E$40</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$39</f>
+              <f>'Heure par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$39</f>
+              <f>'Heure par heure'!$F$2:$F$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$39</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$39</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4089,6 +4089,29 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:00</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="F40" s="3">
+        <f>SUM(C40:E40)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4101,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4962,6 +4985,28 @@
       </c>
       <c r="E39" s="3">
         <f>SUM(B39:D39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <f>'Heure par heure'!A40</f>
+        <v/>
+      </c>
+      <c r="B40" s="3">
+        <f>IF('Heure par heure'!C40="","",'Heure par heure'!C40-N('Heure par heure'!C39))</f>
+        <v/>
+      </c>
+      <c r="C40" s="3">
+        <f>IF('Heure par heure'!D40="","",'Heure par heure'!D40-N('Heure par heure'!D39))</f>
+        <v/>
+      </c>
+      <c r="D40" s="3">
+        <f>IF('Heure par heure'!E40="","",'Heure par heure'!E40-N('Heure par heure'!E39))</f>
+        <v/>
+      </c>
+      <c r="E40" s="3">
+        <f>SUM(B40:D40)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$40</f>
+              <f>'Heure par heure'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$40</f>
+              <f>'Heure par heure'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$40</f>
+              <f>'Heure par heure'!$E$2:$E$41</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$40</f>
+              <f>'Heure par heure'!$B$2:$B$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$40</f>
+              <f>'Heure par heure'!$F$2:$F$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$40</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$40</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4112,6 +4112,29 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="F41" s="3">
+        <f>SUM(C41:E41)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4124,7 +4147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5007,6 +5030,28 @@
       </c>
       <c r="E40" s="3">
         <f>SUM(B40:D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <f>'Heure par heure'!A41</f>
+        <v/>
+      </c>
+      <c r="B41" s="3">
+        <f>IF('Heure par heure'!C41="","",'Heure par heure'!C41-N('Heure par heure'!C40))</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>IF('Heure par heure'!D41="","",'Heure par heure'!D41-N('Heure par heure'!D40))</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>IF('Heure par heure'!E41="","",'Heure par heure'!E41-N('Heure par heure'!E40))</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(B41:D41)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$41</f>
+              <f>'Heure par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$41</f>
+              <f>'Heure par heure'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$41</f>
+              <f>'Heure par heure'!$E$2:$E$42</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$41</f>
+              <f>'Heure par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$41</f>
+              <f>'Heure par heure'!$F$2:$F$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$41</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4135,6 +4135,29 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:00</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F42" s="3">
+        <f>SUM(C42:E42)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4147,7 +4170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5052,6 +5075,28 @@
       </c>
       <c r="E41" s="3">
         <f>SUM(B41:D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <f>'Heure par heure'!A42</f>
+        <v/>
+      </c>
+      <c r="B42" s="3">
+        <f>IF('Heure par heure'!C42="","",'Heure par heure'!C42-N('Heure par heure'!C41))</f>
+        <v/>
+      </c>
+      <c r="C42" s="3">
+        <f>IF('Heure par heure'!D42="","",'Heure par heure'!D42-N('Heure par heure'!D41))</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>IF('Heure par heure'!E42="","",'Heure par heure'!E42-N('Heure par heure'!E41))</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(B42:D42)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$42</f>
+              <f>'Heure par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$42</f>
+              <f>'Heure par heure'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$42</f>
+              <f>'Heure par heure'!$E$2:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$42</f>
+              <f>'Heure par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$42</f>
+              <f>'Heure par heure'!$F$2:$F$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$42</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4158,6 +4158,29 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:00</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F43" s="3">
+        <f>SUM(C43:E43)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4170,7 +4193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5097,6 +5120,28 @@
       </c>
       <c r="E42" s="3">
         <f>SUM(B42:D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <f>'Heure par heure'!A43</f>
+        <v/>
+      </c>
+      <c r="B43" s="3">
+        <f>IF('Heure par heure'!C43="","",'Heure par heure'!C43-N('Heure par heure'!C42))</f>
+        <v/>
+      </c>
+      <c r="C43" s="3">
+        <f>IF('Heure par heure'!D43="","",'Heure par heure'!D43-N('Heure par heure'!D42))</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>IF('Heure par heure'!E43="","",'Heure par heure'!E43-N('Heure par heure'!E42))</f>
+        <v/>
+      </c>
+      <c r="E43" s="3">
+        <f>SUM(B43:D43)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$43</f>
+              <f>'Heure par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$43</f>
+              <f>'Heure par heure'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$43</f>
+              <f>'Heure par heure'!$E$2:$E$44</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$43</f>
+              <f>'Heure par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$43</f>
+              <f>'Heure par heure'!$F$2:$F$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$43</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4181,6 +4181,29 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 06:00</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F44" s="3">
+        <f>SUM(C44:E44)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4193,7 +4216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5142,6 +5165,28 @@
       </c>
       <c r="E43" s="3">
         <f>SUM(B43:D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <f>'Heure par heure'!A44</f>
+        <v/>
+      </c>
+      <c r="B44" s="3">
+        <f>IF('Heure par heure'!C44="","",'Heure par heure'!C44-N('Heure par heure'!C43))</f>
+        <v/>
+      </c>
+      <c r="C44" s="3">
+        <f>IF('Heure par heure'!D44="","",'Heure par heure'!D44-N('Heure par heure'!D43))</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>IF('Heure par heure'!E44="","",'Heure par heure'!E44-N('Heure par heure'!E43))</f>
+        <v/>
+      </c>
+      <c r="E44" s="3">
+        <f>SUM(B44:D44)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$44</f>
+              <f>'Heure par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$44</f>
+              <f>'Heure par heure'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$44</f>
+              <f>'Heure par heure'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$44</f>
+              <f>'Heure par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$44</f>
+              <f>'Heure par heure'!$F$2:$F$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$44</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4204,6 +4204,29 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:00</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="F45" s="3">
+        <f>SUM(C45:E45)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4216,7 +4239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5187,6 +5210,28 @@
       </c>
       <c r="E44" s="3">
         <f>SUM(B44:D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <f>'Heure par heure'!A45</f>
+        <v/>
+      </c>
+      <c r="B45" s="3">
+        <f>IF('Heure par heure'!C45="","",'Heure par heure'!C45-N('Heure par heure'!C44))</f>
+        <v/>
+      </c>
+      <c r="C45" s="3">
+        <f>IF('Heure par heure'!D45="","",'Heure par heure'!D45-N('Heure par heure'!D44))</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>IF('Heure par heure'!E45="","",'Heure par heure'!E45-N('Heure par heure'!E44))</f>
+        <v/>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(B45:D45)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$45</f>
+              <f>'Heure par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$45</f>
+              <f>'Heure par heure'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$45</f>
+              <f>'Heure par heure'!$E$2:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$45</f>
+              <f>'Heure par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$45</f>
+              <f>'Heure par heure'!$F$2:$F$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$45</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3286,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4227,6 +4227,29 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:00</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F46" s="3">
+        <f>SUM(C46:E46)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4239,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5232,6 +5255,28 @@
       </c>
       <c r="E45" s="3">
         <f>SUM(B45:D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <f>'Heure par heure'!A46</f>
+        <v/>
+      </c>
+      <c r="B46" s="3">
+        <f>IF('Heure par heure'!C46="","",'Heure par heure'!C46-N('Heure par heure'!C45))</f>
+        <v/>
+      </c>
+      <c r="C46" s="3">
+        <f>IF('Heure par heure'!D46="","",'Heure par heure'!D46-N('Heure par heure'!D45))</f>
+        <v/>
+      </c>
+      <c r="D46" s="3">
+        <f>IF('Heure par heure'!E46="","",'Heure par heure'!E46-N('Heure par heure'!E45))</f>
+        <v/>
+      </c>
+      <c r="E46" s="3">
+        <f>SUM(B46:D46)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$4</f>
+              <f>'Jour par jour'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$4</f>
+              <f>'Jour par jour'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$4</f>
+              <f>'Jour par jour'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$4</f>
+              <f>'Jour par jour'!$F$2:$F$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$4</f>
+              <f>'Jour par jour'!$H$2:$H$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$4</f>
+              <f>'Jour par jour'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$4</f>
+              <f>'Évolution par vidéo'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1761,12 +1761,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$4</f>
+              <f>'Évolution par vidéo'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$4</f>
+              <f>'Évolution par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1891,12 +1891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1915,12 +1915,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$4</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1939,12 +1939,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$4</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -2157,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2184,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2619,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2837,6 +2837,51 @@
       </c>
       <c r="M4" s="3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <f>IF(ROW()=2,"",B5-B4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="E5" s="3">
+        <f>IF(ROW()=2,D5,D5-D4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2993,10 +3038,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -3039,10 +3084,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1</v>
@@ -3085,7 +3130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3154,6 +3199,22 @@
       </c>
       <c r="D4" s="3" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3168,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3271,6 +3332,29 @@
       </c>
       <c r="E4" s="3">
         <f>SUM(B4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Évolution par vidéo'!B5="","",'Évolution par vidéo'!B5-N('Évolution par vidéo'!B4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>IF('Évolution par vidéo'!C5="","",'Évolution par vidéo'!C5-N('Évolution par vidéo'!C4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>IF('Évolution par vidéo'!D5="","",'Évolution par vidéo'!D5-N('Évolution par vidéo'!D4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(B5:D5)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$46</f>
+              <f>'Heure par heure'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$46</f>
+              <f>'Heure par heure'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$46</f>
+              <f>'Heure par heure'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$46</f>
+              <f>'Heure par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$46</f>
+              <f>'Heure par heure'!$F$2:$F$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$46</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4334,6 +4334,29 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F47" s="3">
+        <f>SUM(C47:E47)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4346,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5361,6 +5384,28 @@
       </c>
       <c r="E46" s="3">
         <f>SUM(B46:D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <f>'Heure par heure'!A47</f>
+        <v/>
+      </c>
+      <c r="B47" s="3">
+        <f>IF('Heure par heure'!C47="","",'Heure par heure'!C47-N('Heure par heure'!C46))</f>
+        <v/>
+      </c>
+      <c r="C47" s="3">
+        <f>IF('Heure par heure'!D47="","",'Heure par heure'!D47-N('Heure par heure'!D46))</f>
+        <v/>
+      </c>
+      <c r="D47" s="3">
+        <f>IF('Heure par heure'!E47="","",'Heure par heure'!E47-N('Heure par heure'!E46))</f>
+        <v/>
+      </c>
+      <c r="E47" s="3">
+        <f>SUM(B47:D47)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$47</f>
+              <f>'Heure par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$47</f>
+              <f>'Heure par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$47</f>
+              <f>'Heure par heure'!$E$2:$E$48</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$47</f>
+              <f>'Heure par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$47</f>
+              <f>'Heure par heure'!$F$2:$F$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4357,6 +4357,29 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F48" s="3">
+        <f>SUM(C48:E48)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4369,7 +4392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5406,6 +5429,28 @@
       </c>
       <c r="E47" s="3">
         <f>SUM(B47:D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <f>'Heure par heure'!A48</f>
+        <v/>
+      </c>
+      <c r="B48" s="3">
+        <f>IF('Heure par heure'!C48="","",'Heure par heure'!C48-N('Heure par heure'!C47))</f>
+        <v/>
+      </c>
+      <c r="C48" s="3">
+        <f>IF('Heure par heure'!D48="","",'Heure par heure'!D48-N('Heure par heure'!D47))</f>
+        <v/>
+      </c>
+      <c r="D48" s="3">
+        <f>IF('Heure par heure'!E48="","",'Heure par heure'!E48-N('Heure par heure'!E47))</f>
+        <v/>
+      </c>
+      <c r="E48" s="3">
+        <f>SUM(B48:D48)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$48</f>
+              <f>'Heure par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$48</f>
+              <f>'Heure par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$48</f>
+              <f>'Heure par heure'!$E$2:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$48</f>
+              <f>'Heure par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$48</f>
+              <f>'Heure par heure'!$F$2:$F$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4380,6 +4380,29 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F49" s="3">
+        <f>SUM(C49:E49)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4392,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5451,6 +5474,28 @@
       </c>
       <c r="E48" s="3">
         <f>SUM(B48:D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <f>'Heure par heure'!A49</f>
+        <v/>
+      </c>
+      <c r="B49" s="3">
+        <f>IF('Heure par heure'!C49="","",'Heure par heure'!C49-N('Heure par heure'!C48))</f>
+        <v/>
+      </c>
+      <c r="C49" s="3">
+        <f>IF('Heure par heure'!D49="","",'Heure par heure'!D49-N('Heure par heure'!D48))</f>
+        <v/>
+      </c>
+      <c r="D49" s="3">
+        <f>IF('Heure par heure'!E49="","",'Heure par heure'!E49-N('Heure par heure'!E48))</f>
+        <v/>
+      </c>
+      <c r="E49" s="3">
+        <f>SUM(B49:D49)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$49</f>
+              <f>'Heure par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$49</f>
+              <f>'Heure par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$49</f>
+              <f>'Heure par heure'!$E$2:$E$50</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$49</f>
+              <f>'Heure par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$49</f>
+              <f>'Heure par heure'!$F$2:$F$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4403,6 +4403,29 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F50" s="3">
+        <f>SUM(C50:E50)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4415,7 +4438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5496,6 +5519,28 @@
       </c>
       <c r="E49" s="3">
         <f>SUM(B49:D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <f>'Heure par heure'!A50</f>
+        <v/>
+      </c>
+      <c r="B50" s="3">
+        <f>IF('Heure par heure'!C50="","",'Heure par heure'!C50-N('Heure par heure'!C49))</f>
+        <v/>
+      </c>
+      <c r="C50" s="3">
+        <f>IF('Heure par heure'!D50="","",'Heure par heure'!D50-N('Heure par heure'!D49))</f>
+        <v/>
+      </c>
+      <c r="D50" s="3">
+        <f>IF('Heure par heure'!E50="","",'Heure par heure'!E50-N('Heure par heure'!E49))</f>
+        <v/>
+      </c>
+      <c r="E50" s="3">
+        <f>SUM(B50:D50)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$50</f>
+              <f>'Heure par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$50</f>
+              <f>'Heure par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$50</f>
+              <f>'Heure par heure'!$E$2:$E$51</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$50</f>
+              <f>'Heure par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$50</f>
+              <f>'Heure par heure'!$F$2:$F$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4426,6 +4426,29 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:00</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F51" s="3">
+        <f>SUM(C51:E51)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4438,7 +4461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5541,6 +5564,28 @@
       </c>
       <c r="E50" s="3">
         <f>SUM(B50:D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <f>'Heure par heure'!A51</f>
+        <v/>
+      </c>
+      <c r="B51" s="3">
+        <f>IF('Heure par heure'!C51="","",'Heure par heure'!C51-N('Heure par heure'!C50))</f>
+        <v/>
+      </c>
+      <c r="C51" s="3">
+        <f>IF('Heure par heure'!D51="","",'Heure par heure'!D51-N('Heure par heure'!D50))</f>
+        <v/>
+      </c>
+      <c r="D51" s="3">
+        <f>IF('Heure par heure'!E51="","",'Heure par heure'!E51-N('Heure par heure'!E50))</f>
+        <v/>
+      </c>
+      <c r="E51" s="3">
+        <f>SUM(B51:D51)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$51</f>
+              <f>'Heure par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$51</f>
+              <f>'Heure par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$51</f>
+              <f>'Heure par heure'!$E$2:$E$52</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$51</f>
+              <f>'Heure par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$51</f>
+              <f>'Heure par heure'!$F$2:$F$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4449,6 +4449,29 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F52" s="3">
+        <f>SUM(C52:E52)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4461,7 +4484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5586,6 +5609,28 @@
       </c>
       <c r="E51" s="3">
         <f>SUM(B51:D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <f>'Heure par heure'!A52</f>
+        <v/>
+      </c>
+      <c r="B52" s="3">
+        <f>IF('Heure par heure'!C52="","",'Heure par heure'!C52-N('Heure par heure'!C51))</f>
+        <v/>
+      </c>
+      <c r="C52" s="3">
+        <f>IF('Heure par heure'!D52="","",'Heure par heure'!D52-N('Heure par heure'!D51))</f>
+        <v/>
+      </c>
+      <c r="D52" s="3">
+        <f>IF('Heure par heure'!E52="","",'Heure par heure'!E52-N('Heure par heure'!E51))</f>
+        <v/>
+      </c>
+      <c r="E52" s="3">
+        <f>SUM(B52:D52)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$52</f>
+              <f>'Heure par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$52</f>
+              <f>'Heure par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$52</f>
+              <f>'Heure par heure'!$E$2:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$52</f>
+              <f>'Heure par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$52</f>
+              <f>'Heure par heure'!$F$2:$F$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4472,6 +4472,29 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F53" s="3">
+        <f>SUM(C53:E53)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4484,7 +4507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5631,6 +5654,28 @@
       </c>
       <c r="E52" s="3">
         <f>SUM(B52:D52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <f>'Heure par heure'!A53</f>
+        <v/>
+      </c>
+      <c r="B53" s="3">
+        <f>IF('Heure par heure'!C53="","",'Heure par heure'!C53-N('Heure par heure'!C52))</f>
+        <v/>
+      </c>
+      <c r="C53" s="3">
+        <f>IF('Heure par heure'!D53="","",'Heure par heure'!D53-N('Heure par heure'!D52))</f>
+        <v/>
+      </c>
+      <c r="D53" s="3">
+        <f>IF('Heure par heure'!E53="","",'Heure par heure'!E53-N('Heure par heure'!E52))</f>
+        <v/>
+      </c>
+      <c r="E53" s="3">
+        <f>SUM(B53:D53)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$53</f>
+              <f>'Heure par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$53</f>
+              <f>'Heure par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$53</f>
+              <f>'Heure par heure'!$E$2:$E$54</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$53</f>
+              <f>'Heure par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$53</f>
+              <f>'Heure par heure'!$F$2:$F$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4495,6 +4495,29 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F54" s="3">
+        <f>SUM(C54:E54)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4507,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5676,6 +5699,28 @@
       </c>
       <c r="E53" s="3">
         <f>SUM(B53:D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <f>'Heure par heure'!A54</f>
+        <v/>
+      </c>
+      <c r="B54" s="3">
+        <f>IF('Heure par heure'!C54="","",'Heure par heure'!C54-N('Heure par heure'!C53))</f>
+        <v/>
+      </c>
+      <c r="C54" s="3">
+        <f>IF('Heure par heure'!D54="","",'Heure par heure'!D54-N('Heure par heure'!D53))</f>
+        <v/>
+      </c>
+      <c r="D54" s="3">
+        <f>IF('Heure par heure'!E54="","",'Heure par heure'!E54-N('Heure par heure'!E53))</f>
+        <v/>
+      </c>
+      <c r="E54" s="3">
+        <f>SUM(B54:D54)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$54</f>
+              <f>'Heure par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$54</f>
+              <f>'Heure par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$54</f>
+              <f>'Heure par heure'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$54</f>
+              <f>'Heure par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$54</f>
+              <f>'Heure par heure'!$F$2:$F$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4518,6 +4518,29 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:00</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F55" s="3">
+        <f>SUM(C55:E55)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4530,7 +4553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5721,6 +5744,28 @@
       </c>
       <c r="E54" s="3">
         <f>SUM(B54:D54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <f>'Heure par heure'!A55</f>
+        <v/>
+      </c>
+      <c r="B55" s="3">
+        <f>IF('Heure par heure'!C55="","",'Heure par heure'!C55-N('Heure par heure'!C54))</f>
+        <v/>
+      </c>
+      <c r="C55" s="3">
+        <f>IF('Heure par heure'!D55="","",'Heure par heure'!D55-N('Heure par heure'!D54))</f>
+        <v/>
+      </c>
+      <c r="D55" s="3">
+        <f>IF('Heure par heure'!E55="","",'Heure par heure'!E55-N('Heure par heure'!E54))</f>
+        <v/>
+      </c>
+      <c r="E55" s="3">
+        <f>SUM(B55:D55)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$55</f>
+              <f>'Heure par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$55</f>
+              <f>'Heure par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$55</f>
+              <f>'Heure par heure'!$E$2:$E$56</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$55</f>
+              <f>'Heure par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$55</f>
+              <f>'Heure par heure'!$F$2:$F$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4541,6 +4541,29 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:00</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F56" s="3">
+        <f>SUM(C56:E56)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4553,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5766,6 +5789,28 @@
       </c>
       <c r="E55" s="3">
         <f>SUM(B55:D55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <f>'Heure par heure'!A56</f>
+        <v/>
+      </c>
+      <c r="B56" s="3">
+        <f>IF('Heure par heure'!C56="","",'Heure par heure'!C56-N('Heure par heure'!C55))</f>
+        <v/>
+      </c>
+      <c r="C56" s="3">
+        <f>IF('Heure par heure'!D56="","",'Heure par heure'!D56-N('Heure par heure'!D55))</f>
+        <v/>
+      </c>
+      <c r="D56" s="3">
+        <f>IF('Heure par heure'!E56="","",'Heure par heure'!E56-N('Heure par heure'!E55))</f>
+        <v/>
+      </c>
+      <c r="E56" s="3">
+        <f>SUM(B56:D56)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$56</f>
+              <f>'Heure par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$56</f>
+              <f>'Heure par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$56</f>
+              <f>'Heure par heure'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$56</f>
+              <f>'Heure par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$56</f>
+              <f>'Heure par heure'!$F$2:$F$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4564,6 +4564,29 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:00</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F57" s="3">
+        <f>SUM(C57:E57)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4576,7 +4599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5811,6 +5834,28 @@
       </c>
       <c r="E56" s="3">
         <f>SUM(B56:D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <f>'Heure par heure'!A57</f>
+        <v/>
+      </c>
+      <c r="B57" s="3">
+        <f>IF('Heure par heure'!C57="","",'Heure par heure'!C57-N('Heure par heure'!C56))</f>
+        <v/>
+      </c>
+      <c r="C57" s="3">
+        <f>IF('Heure par heure'!D57="","",'Heure par heure'!D57-N('Heure par heure'!D56))</f>
+        <v/>
+      </c>
+      <c r="D57" s="3">
+        <f>IF('Heure par heure'!E57="","",'Heure par heure'!E57-N('Heure par heure'!E56))</f>
+        <v/>
+      </c>
+      <c r="E57" s="3">
+        <f>SUM(B57:D57)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$57</f>
+              <f>'Heure par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$57</f>
+              <f>'Heure par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$57</f>
+              <f>'Heure par heure'!$E$2:$E$58</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$57</f>
+              <f>'Heure par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$57</f>
+              <f>'Heure par heure'!$F$2:$F$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4587,6 +4587,29 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:00</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F58" s="3">
+        <f>SUM(C58:E58)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4599,7 +4622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5856,6 +5879,28 @@
       </c>
       <c r="E57" s="3">
         <f>SUM(B57:D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <f>'Heure par heure'!A58</f>
+        <v/>
+      </c>
+      <c r="B58" s="3">
+        <f>IF('Heure par heure'!C58="","",'Heure par heure'!C58-N('Heure par heure'!C57))</f>
+        <v/>
+      </c>
+      <c r="C58" s="3">
+        <f>IF('Heure par heure'!D58="","",'Heure par heure'!D58-N('Heure par heure'!D57))</f>
+        <v/>
+      </c>
+      <c r="D58" s="3">
+        <f>IF('Heure par heure'!E58="","",'Heure par heure'!E58-N('Heure par heure'!E57))</f>
+        <v/>
+      </c>
+      <c r="E58" s="3">
+        <f>SUM(B58:D58)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$58</f>
+              <f>'Heure par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$58</f>
+              <f>'Heure par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$58</f>
+              <f>'Heure par heure'!$E$2:$E$59</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$58</f>
+              <f>'Heure par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$58</f>
+              <f>'Heure par heure'!$F$2:$F$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4610,6 +4610,29 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F59" s="3">
+        <f>SUM(C59:E59)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4622,7 +4645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5901,6 +5924,28 @@
       </c>
       <c r="E58" s="3">
         <f>SUM(B58:D58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <f>'Heure par heure'!A59</f>
+        <v/>
+      </c>
+      <c r="B59" s="3">
+        <f>IF('Heure par heure'!C59="","",'Heure par heure'!C59-N('Heure par heure'!C58))</f>
+        <v/>
+      </c>
+      <c r="C59" s="3">
+        <f>IF('Heure par heure'!D59="","",'Heure par heure'!D59-N('Heure par heure'!D58))</f>
+        <v/>
+      </c>
+      <c r="D59" s="3">
+        <f>IF('Heure par heure'!E59="","",'Heure par heure'!E59-N('Heure par heure'!E58))</f>
+        <v/>
+      </c>
+      <c r="E59" s="3">
+        <f>SUM(B59:D59)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$59</f>
+              <f>'Heure par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$59</f>
+              <f>'Heure par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$59</f>
+              <f>'Heure par heure'!$E$2:$E$60</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$59</f>
+              <f>'Heure par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$59</f>
+              <f>'Heure par heure'!$F$2:$F$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4633,6 +4633,29 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:00</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F60" s="3">
+        <f>SUM(C60:E60)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4645,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5946,6 +5969,28 @@
       </c>
       <c r="E59" s="3">
         <f>SUM(B59:D59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <f>'Heure par heure'!A60</f>
+        <v/>
+      </c>
+      <c r="B60" s="3">
+        <f>IF('Heure par heure'!C60="","",'Heure par heure'!C60-N('Heure par heure'!C59))</f>
+        <v/>
+      </c>
+      <c r="C60" s="3">
+        <f>IF('Heure par heure'!D60="","",'Heure par heure'!D60-N('Heure par heure'!D59))</f>
+        <v/>
+      </c>
+      <c r="D60" s="3">
+        <f>IF('Heure par heure'!E60="","",'Heure par heure'!E60-N('Heure par heure'!E59))</f>
+        <v/>
+      </c>
+      <c r="E60" s="3">
+        <f>SUM(B60:D60)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$60</f>
+              <f>'Heure par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$60</f>
+              <f>'Heure par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$60</f>
+              <f>'Heure par heure'!$E$2:$E$61</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$60</f>
+              <f>'Heure par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$60</f>
+              <f>'Heure par heure'!$F$2:$F$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4656,6 +4656,29 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:00</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F61" s="3">
+        <f>SUM(C61:E61)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4668,7 +4691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5991,6 +6014,28 @@
       </c>
       <c r="E60" s="3">
         <f>SUM(B60:D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <f>'Heure par heure'!A61</f>
+        <v/>
+      </c>
+      <c r="B61" s="3">
+        <f>IF('Heure par heure'!C61="","",'Heure par heure'!C61-N('Heure par heure'!C60))</f>
+        <v/>
+      </c>
+      <c r="C61" s="3">
+        <f>IF('Heure par heure'!D61="","",'Heure par heure'!D61-N('Heure par heure'!D60))</f>
+        <v/>
+      </c>
+      <c r="D61" s="3">
+        <f>IF('Heure par heure'!E61="","",'Heure par heure'!E61-N('Heure par heure'!E60))</f>
+        <v/>
+      </c>
+      <c r="E61" s="3">
+        <f>SUM(B61:D61)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$61</f>
+              <f>'Heure par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$61</f>
+              <f>'Heure par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$61</f>
+              <f>'Heure par heure'!$E$2:$E$62</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$61</f>
+              <f>'Heure par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$61</f>
+              <f>'Heure par heure'!$F$2:$F$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4679,6 +4679,29 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:00</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F62" s="3">
+        <f>SUM(C62:E62)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4691,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6036,6 +6059,28 @@
       </c>
       <c r="E61" s="3">
         <f>SUM(B61:D61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <f>'Heure par heure'!A62</f>
+        <v/>
+      </c>
+      <c r="B62" s="3">
+        <f>IF('Heure par heure'!C62="","",'Heure par heure'!C62-N('Heure par heure'!C61))</f>
+        <v/>
+      </c>
+      <c r="C62" s="3">
+        <f>IF('Heure par heure'!D62="","",'Heure par heure'!D62-N('Heure par heure'!D61))</f>
+        <v/>
+      </c>
+      <c r="D62" s="3">
+        <f>IF('Heure par heure'!E62="","",'Heure par heure'!E62-N('Heure par heure'!E61))</f>
+        <v/>
+      </c>
+      <c r="E62" s="3">
+        <f>SUM(B62:D62)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$62</f>
+              <f>'Heure par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$62</f>
+              <f>'Heure par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$62</f>
+              <f>'Heure par heure'!$E$2:$E$63</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$62</f>
+              <f>'Heure par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$62</f>
+              <f>'Heure par heure'!$F$2:$F$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4702,6 +4702,29 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 08:00</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F63" s="3">
+        <f>SUM(C63:E63)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4714,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6081,6 +6104,28 @@
       </c>
       <c r="E62" s="3">
         <f>SUM(B62:D62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <f>'Heure par heure'!A63</f>
+        <v/>
+      </c>
+      <c r="B63" s="3">
+        <f>IF('Heure par heure'!C63="","",'Heure par heure'!C63-N('Heure par heure'!C62))</f>
+        <v/>
+      </c>
+      <c r="C63" s="3">
+        <f>IF('Heure par heure'!D63="","",'Heure par heure'!D63-N('Heure par heure'!D62))</f>
+        <v/>
+      </c>
+      <c r="D63" s="3">
+        <f>IF('Heure par heure'!E63="","",'Heure par heure'!E63-N('Heure par heure'!E62))</f>
+        <v/>
+      </c>
+      <c r="E63" s="3">
+        <f>SUM(B63:D63)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$5</f>
+              <f>'Jour par jour'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$5</f>
+              <f>'Jour par jour'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$5</f>
+              <f>'Jour par jour'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$5</f>
+              <f>'Jour par jour'!$F$2:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$5</f>
+              <f>'Jour par jour'!$H$2:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$5</f>
+              <f>'Jour par jour'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$5</f>
+              <f>'Évolution par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1761,12 +1761,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$5</f>
+              <f>'Évolution par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$5</f>
+              <f>'Évolution par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -1891,12 +1891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1915,12 +1915,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1939,12 +1939,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -2157,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2184,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2619,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2881,6 +2881,51 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <f>IF(ROW()=2,"",B6-B5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="E6" s="3">
+        <f>IF(ROW()=2,D6,D6-D5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3130,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3214,6 +3259,22 @@
         <v>203</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>94</v>
       </c>
     </row>
@@ -3229,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3355,6 +3416,29 @@
       </c>
       <c r="E5" s="3">
         <f>SUM(B5:D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Évolution par vidéo'!B6="","",'Évolution par vidéo'!B6-N('Évolution par vidéo'!B5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>IF('Évolution par vidéo'!C6="","",'Évolution par vidéo'!C6-N('Évolution par vidéo'!C5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>IF('Évolution par vidéo'!D6="","",'Évolution par vidéo'!D6-N('Évolution par vidéo'!D5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$63</f>
+              <f>'Heure par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$63</f>
+              <f>'Heure par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$63</f>
+              <f>'Heure par heure'!$E$2:$E$64</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$63</f>
+              <f>'Heure par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$63</f>
+              <f>'Heure par heure'!$F$2:$F$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4809,6 +4809,29 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:00</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F64" s="3">
+        <f>SUM(C64:E64)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4821,7 +4844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6210,6 +6233,28 @@
       </c>
       <c r="E63" s="3">
         <f>SUM(B63:D63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <f>'Heure par heure'!A64</f>
+        <v/>
+      </c>
+      <c r="B64" s="3">
+        <f>IF('Heure par heure'!C64="","",'Heure par heure'!C64-N('Heure par heure'!C63))</f>
+        <v/>
+      </c>
+      <c r="C64" s="3">
+        <f>IF('Heure par heure'!D64="","",'Heure par heure'!D64-N('Heure par heure'!D63))</f>
+        <v/>
+      </c>
+      <c r="D64" s="3">
+        <f>IF('Heure par heure'!E64="","",'Heure par heure'!E64-N('Heure par heure'!E63))</f>
+        <v/>
+      </c>
+      <c r="E64" s="3">
+        <f>SUM(B64:D64)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$64</f>
+              <f>'Heure par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$64</f>
+              <f>'Heure par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$64</f>
+              <f>'Heure par heure'!$E$2:$E$65</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$64</f>
+              <f>'Heure par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$64</f>
+              <f>'Heure par heure'!$F$2:$F$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4832,6 +4832,29 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:00</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F65" s="3">
+        <f>SUM(C65:E65)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4844,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6255,6 +6278,28 @@
       </c>
       <c r="E64" s="3">
         <f>SUM(B64:D64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <f>'Heure par heure'!A65</f>
+        <v/>
+      </c>
+      <c r="B65" s="3">
+        <f>IF('Heure par heure'!C65="","",'Heure par heure'!C65-N('Heure par heure'!C64))</f>
+        <v/>
+      </c>
+      <c r="C65" s="3">
+        <f>IF('Heure par heure'!D65="","",'Heure par heure'!D65-N('Heure par heure'!D64))</f>
+        <v/>
+      </c>
+      <c r="D65" s="3">
+        <f>IF('Heure par heure'!E65="","",'Heure par heure'!E65-N('Heure par heure'!E64))</f>
+        <v/>
+      </c>
+      <c r="E65" s="3">
+        <f>SUM(B65:D65)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$65</f>
+              <f>'Heure par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$65</f>
+              <f>'Heure par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$65</f>
+              <f>'Heure par heure'!$E$2:$E$66</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$65</f>
+              <f>'Heure par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$65</f>
+              <f>'Heure par heure'!$F$2:$F$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4855,6 +4855,29 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F66" s="3">
+        <f>SUM(C66:E66)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4867,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6300,6 +6323,28 @@
       </c>
       <c r="E65" s="3">
         <f>SUM(B65:D65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <f>'Heure par heure'!A66</f>
+        <v/>
+      </c>
+      <c r="B66" s="3">
+        <f>IF('Heure par heure'!C66="","",'Heure par heure'!C66-N('Heure par heure'!C65))</f>
+        <v/>
+      </c>
+      <c r="C66" s="3">
+        <f>IF('Heure par heure'!D66="","",'Heure par heure'!D66-N('Heure par heure'!D65))</f>
+        <v/>
+      </c>
+      <c r="D66" s="3">
+        <f>IF('Heure par heure'!E66="","",'Heure par heure'!E66-N('Heure par heure'!E65))</f>
+        <v/>
+      </c>
+      <c r="E66" s="3">
+        <f>SUM(B66:D66)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$66</f>
+              <f>'Heure par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$66</f>
+              <f>'Heure par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$66</f>
+              <f>'Heure par heure'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$66</f>
+              <f>'Heure par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$66</f>
+              <f>'Heure par heure'!$F$2:$F$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4878,6 +4878,29 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:00</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F67" s="3">
+        <f>SUM(C67:E67)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4890,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6345,6 +6368,28 @@
       </c>
       <c r="E66" s="3">
         <f>SUM(B66:D66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <f>'Heure par heure'!A67</f>
+        <v/>
+      </c>
+      <c r="B67" s="3">
+        <f>IF('Heure par heure'!C67="","",'Heure par heure'!C67-N('Heure par heure'!C66))</f>
+        <v/>
+      </c>
+      <c r="C67" s="3">
+        <f>IF('Heure par heure'!D67="","",'Heure par heure'!D67-N('Heure par heure'!D66))</f>
+        <v/>
+      </c>
+      <c r="D67" s="3">
+        <f>IF('Heure par heure'!E67="","",'Heure par heure'!E67-N('Heure par heure'!E66))</f>
+        <v/>
+      </c>
+      <c r="E67" s="3">
+        <f>SUM(B67:D67)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$67</f>
+              <f>'Heure par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$67</f>
+              <f>'Heure par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$67</f>
+              <f>'Heure par heure'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$67</f>
+              <f>'Heure par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$67</f>
+              <f>'Heure par heure'!$F$2:$F$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4901,6 +4901,29 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F68" s="3">
+        <f>SUM(C68:E68)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4913,7 +4936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6390,6 +6413,28 @@
       </c>
       <c r="E67" s="3">
         <f>SUM(B67:D67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <f>'Heure par heure'!A68</f>
+        <v/>
+      </c>
+      <c r="B68" s="3">
+        <f>IF('Heure par heure'!C68="","",'Heure par heure'!C68-N('Heure par heure'!C67))</f>
+        <v/>
+      </c>
+      <c r="C68" s="3">
+        <f>IF('Heure par heure'!D68="","",'Heure par heure'!D68-N('Heure par heure'!D67))</f>
+        <v/>
+      </c>
+      <c r="D68" s="3">
+        <f>IF('Heure par heure'!E68="","",'Heure par heure'!E68-N('Heure par heure'!E67))</f>
+        <v/>
+      </c>
+      <c r="E68" s="3">
+        <f>SUM(B68:D68)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$68</f>
+              <f>'Heure par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$68</f>
+              <f>'Heure par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$68</f>
+              <f>'Heure par heure'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$68</f>
+              <f>'Heure par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$68</f>
+              <f>'Heure par heure'!$F$2:$F$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4924,6 +4924,29 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F69" s="3">
+        <f>SUM(C69:E69)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4936,7 +4959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6435,6 +6458,28 @@
       </c>
       <c r="E68" s="3">
         <f>SUM(B68:D68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <f>'Heure par heure'!A69</f>
+        <v/>
+      </c>
+      <c r="B69" s="3">
+        <f>IF('Heure par heure'!C69="","",'Heure par heure'!C69-N('Heure par heure'!C68))</f>
+        <v/>
+      </c>
+      <c r="C69" s="3">
+        <f>IF('Heure par heure'!D69="","",'Heure par heure'!D69-N('Heure par heure'!D68))</f>
+        <v/>
+      </c>
+      <c r="D69" s="3">
+        <f>IF('Heure par heure'!E69="","",'Heure par heure'!E69-N('Heure par heure'!E68))</f>
+        <v/>
+      </c>
+      <c r="E69" s="3">
+        <f>SUM(B69:D69)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$69</f>
+              <f>'Heure par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$69</f>
+              <f>'Heure par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$69</f>
+              <f>'Heure par heure'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$69</f>
+              <f>'Heure par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$69</f>
+              <f>'Heure par heure'!$F$2:$F$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4947,6 +4947,29 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:00</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F70" s="3">
+        <f>SUM(C70:E70)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4959,7 +4982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6480,6 +6503,28 @@
       </c>
       <c r="E69" s="3">
         <f>SUM(B69:D69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <f>'Heure par heure'!A70</f>
+        <v/>
+      </c>
+      <c r="B70" s="3">
+        <f>IF('Heure par heure'!C70="","",'Heure par heure'!C70-N('Heure par heure'!C69))</f>
+        <v/>
+      </c>
+      <c r="C70" s="3">
+        <f>IF('Heure par heure'!D70="","",'Heure par heure'!D70-N('Heure par heure'!D69))</f>
+        <v/>
+      </c>
+      <c r="D70" s="3">
+        <f>IF('Heure par heure'!E70="","",'Heure par heure'!E70-N('Heure par heure'!E69))</f>
+        <v/>
+      </c>
+      <c r="E70" s="3">
+        <f>SUM(B70:D70)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$70</f>
+              <f>'Heure par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$70</f>
+              <f>'Heure par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$70</f>
+              <f>'Heure par heure'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$70</f>
+              <f>'Heure par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$70</f>
+              <f>'Heure par heure'!$F$2:$F$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4970,6 +4970,29 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 16:00</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F71" s="3">
+        <f>SUM(C71:E71)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4982,7 +5005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6525,6 +6548,28 @@
       </c>
       <c r="E70" s="3">
         <f>SUM(B70:D70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <f>'Heure par heure'!A71</f>
+        <v/>
+      </c>
+      <c r="B71" s="3">
+        <f>IF('Heure par heure'!C71="","",'Heure par heure'!C71-N('Heure par heure'!C70))</f>
+        <v/>
+      </c>
+      <c r="C71" s="3">
+        <f>IF('Heure par heure'!D71="","",'Heure par heure'!D71-N('Heure par heure'!D70))</f>
+        <v/>
+      </c>
+      <c r="D71" s="3">
+        <f>IF('Heure par heure'!E71="","",'Heure par heure'!E71-N('Heure par heure'!E70))</f>
+        <v/>
+      </c>
+      <c r="E71" s="3">
+        <f>SUM(B71:D71)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$71</f>
+              <f>'Heure par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$71</f>
+              <f>'Heure par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$71</f>
+              <f>'Heure par heure'!$E$2:$E$72</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$71</f>
+              <f>'Heure par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$71</f>
+              <f>'Heure par heure'!$F$2:$F$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4993,6 +4993,29 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:00</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F72" s="3">
+        <f>SUM(C72:E72)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5005,7 +5028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6570,6 +6593,28 @@
       </c>
       <c r="E71" s="3">
         <f>SUM(B71:D71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <f>'Heure par heure'!A72</f>
+        <v/>
+      </c>
+      <c r="B72" s="3">
+        <f>IF('Heure par heure'!C72="","",'Heure par heure'!C72-N('Heure par heure'!C71))</f>
+        <v/>
+      </c>
+      <c r="C72" s="3">
+        <f>IF('Heure par heure'!D72="","",'Heure par heure'!D72-N('Heure par heure'!D71))</f>
+        <v/>
+      </c>
+      <c r="D72" s="3">
+        <f>IF('Heure par heure'!E72="","",'Heure par heure'!E72-N('Heure par heure'!E71))</f>
+        <v/>
+      </c>
+      <c r="E72" s="3">
+        <f>SUM(B72:D72)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$72</f>
+              <f>'Heure par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$72</f>
+              <f>'Heure par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$72</f>
+              <f>'Heure par heure'!$E$2:$E$73</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$72</f>
+              <f>'Heure par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$72</f>
+              <f>'Heure par heure'!$F$2:$F$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5016,6 +5016,29 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:00</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F73" s="3">
+        <f>SUM(C73:E73)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5028,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6615,6 +6638,28 @@
       </c>
       <c r="E72" s="3">
         <f>SUM(B72:D72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <f>'Heure par heure'!A73</f>
+        <v/>
+      </c>
+      <c r="B73" s="3">
+        <f>IF('Heure par heure'!C73="","",'Heure par heure'!C73-N('Heure par heure'!C72))</f>
+        <v/>
+      </c>
+      <c r="C73" s="3">
+        <f>IF('Heure par heure'!D73="","",'Heure par heure'!D73-N('Heure par heure'!D72))</f>
+        <v/>
+      </c>
+      <c r="D73" s="3">
+        <f>IF('Heure par heure'!E73="","",'Heure par heure'!E73-N('Heure par heure'!E72))</f>
+        <v/>
+      </c>
+      <c r="E73" s="3">
+        <f>SUM(B73:D73)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$73</f>
+              <f>'Heure par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$73</f>
+              <f>'Heure par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$73</f>
+              <f>'Heure par heure'!$E$2:$E$74</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$73</f>
+              <f>'Heure par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$73</f>
+              <f>'Heure par heure'!$F$2:$F$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5039,6 +5039,29 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:00</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F74" s="3">
+        <f>SUM(C74:E74)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5051,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6660,6 +6683,28 @@
       </c>
       <c r="E73" s="3">
         <f>SUM(B73:D73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <f>'Heure par heure'!A74</f>
+        <v/>
+      </c>
+      <c r="B74" s="3">
+        <f>IF('Heure par heure'!C74="","",'Heure par heure'!C74-N('Heure par heure'!C73))</f>
+        <v/>
+      </c>
+      <c r="C74" s="3">
+        <f>IF('Heure par heure'!D74="","",'Heure par heure'!D74-N('Heure par heure'!D73))</f>
+        <v/>
+      </c>
+      <c r="D74" s="3">
+        <f>IF('Heure par heure'!E74="","",'Heure par heure'!E74-N('Heure par heure'!E73))</f>
+        <v/>
+      </c>
+      <c r="E74" s="3">
+        <f>SUM(B74:D74)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$74</f>
+              <f>'Heure par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$74</f>
+              <f>'Heure par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$74</f>
+              <f>'Heure par heure'!$E$2:$E$75</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$74</f>
+              <f>'Heure par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$74</f>
+              <f>'Heure par heure'!$F$2:$F$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5062,6 +5062,29 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:00</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F75" s="3">
+        <f>SUM(C75:E75)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5074,7 +5097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6705,6 +6728,28 @@
       </c>
       <c r="E74" s="3">
         <f>SUM(B74:D74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <f>'Heure par heure'!A75</f>
+        <v/>
+      </c>
+      <c r="B75" s="3">
+        <f>IF('Heure par heure'!C75="","",'Heure par heure'!C75-N('Heure par heure'!C74))</f>
+        <v/>
+      </c>
+      <c r="C75" s="3">
+        <f>IF('Heure par heure'!D75="","",'Heure par heure'!D75-N('Heure par heure'!D74))</f>
+        <v/>
+      </c>
+      <c r="D75" s="3">
+        <f>IF('Heure par heure'!E75="","",'Heure par heure'!E75-N('Heure par heure'!E74))</f>
+        <v/>
+      </c>
+      <c r="E75" s="3">
+        <f>SUM(B75:D75)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$75</f>
+              <f>'Heure par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$75</f>
+              <f>'Heure par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$75</f>
+              <f>'Heure par heure'!$E$2:$E$76</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$75</f>
+              <f>'Heure par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$75</f>
+              <f>'Heure par heure'!$F$2:$F$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5085,6 +5085,29 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:00</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F76" s="3">
+        <f>SUM(C76:E76)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5097,7 +5120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6750,6 +6773,28 @@
       </c>
       <c r="E75" s="3">
         <f>SUM(B75:D75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <f>'Heure par heure'!A76</f>
+        <v/>
+      </c>
+      <c r="B76" s="3">
+        <f>IF('Heure par heure'!C76="","",'Heure par heure'!C76-N('Heure par heure'!C75))</f>
+        <v/>
+      </c>
+      <c r="C76" s="3">
+        <f>IF('Heure par heure'!D76="","",'Heure par heure'!D76-N('Heure par heure'!D75))</f>
+        <v/>
+      </c>
+      <c r="D76" s="3">
+        <f>IF('Heure par heure'!E76="","",'Heure par heure'!E76-N('Heure par heure'!E75))</f>
+        <v/>
+      </c>
+      <c r="E76" s="3">
+        <f>SUM(B76:D76)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$76</f>
+              <f>'Heure par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$76</f>
+              <f>'Heure par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$76</f>
+              <f>'Heure par heure'!$E$2:$E$77</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$76</f>
+              <f>'Heure par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$76</f>
+              <f>'Heure par heure'!$F$2:$F$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5108,6 +5108,29 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:00</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F77" s="3">
+        <f>SUM(C77:E77)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5120,7 +5143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6795,6 +6818,28 @@
       </c>
       <c r="E76" s="3">
         <f>SUM(B76:D76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <f>'Heure par heure'!A77</f>
+        <v/>
+      </c>
+      <c r="B77" s="3">
+        <f>IF('Heure par heure'!C77="","",'Heure par heure'!C77-N('Heure par heure'!C76))</f>
+        <v/>
+      </c>
+      <c r="C77" s="3">
+        <f>IF('Heure par heure'!D77="","",'Heure par heure'!D77-N('Heure par heure'!D76))</f>
+        <v/>
+      </c>
+      <c r="D77" s="3">
+        <f>IF('Heure par heure'!E77="","",'Heure par heure'!E77-N('Heure par heure'!E76))</f>
+        <v/>
+      </c>
+      <c r="E77" s="3">
+        <f>SUM(B77:D77)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$77</f>
+              <f>'Heure par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$77</f>
+              <f>'Heure par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$77</f>
+              <f>'Heure par heure'!$E$2:$E$78</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$77</f>
+              <f>'Heure par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$77</f>
+              <f>'Heure par heure'!$F$2:$F$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5131,29 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:00</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F78" s="3">
+        <f>SUM(C78:E78)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5143,7 +5166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6840,6 +6863,28 @@
       </c>
       <c r="E77" s="3">
         <f>SUM(B77:D77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <f>'Heure par heure'!A78</f>
+        <v/>
+      </c>
+      <c r="B78" s="3">
+        <f>IF('Heure par heure'!C78="","",'Heure par heure'!C78-N('Heure par heure'!C77))</f>
+        <v/>
+      </c>
+      <c r="C78" s="3">
+        <f>IF('Heure par heure'!D78="","",'Heure par heure'!D78-N('Heure par heure'!D77))</f>
+        <v/>
+      </c>
+      <c r="D78" s="3">
+        <f>IF('Heure par heure'!E78="","",'Heure par heure'!E78-N('Heure par heure'!E77))</f>
+        <v/>
+      </c>
+      <c r="E78" s="3">
+        <f>SUM(B78:D78)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$78</f>
+              <f>'Heure par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$78</f>
+              <f>'Heure par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$78</f>
+              <f>'Heure par heure'!$E$2:$E$79</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$78</f>
+              <f>'Heure par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$78</f>
+              <f>'Heure par heure'!$F$2:$F$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5154,6 +5154,29 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:00</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F79" s="3">
+        <f>SUM(C79:E79)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5166,7 +5189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6885,6 +6908,28 @@
       </c>
       <c r="E78" s="3">
         <f>SUM(B78:D78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <f>'Heure par heure'!A79</f>
+        <v/>
+      </c>
+      <c r="B79" s="3">
+        <f>IF('Heure par heure'!C79="","",'Heure par heure'!C79-N('Heure par heure'!C78))</f>
+        <v/>
+      </c>
+      <c r="C79" s="3">
+        <f>IF('Heure par heure'!D79="","",'Heure par heure'!D79-N('Heure par heure'!D78))</f>
+        <v/>
+      </c>
+      <c r="D79" s="3">
+        <f>IF('Heure par heure'!E79="","",'Heure par heure'!E79-N('Heure par heure'!E78))</f>
+        <v/>
+      </c>
+      <c r="E79" s="3">
+        <f>SUM(B79:D79)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$79</f>
+              <f>'Heure par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$79</f>
+              <f>'Heure par heure'!$D$2:$D$80</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$79</f>
+              <f>'Heure par heure'!$E$2:$E$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$F$2:$F$80</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$79</f>
+              <f>'Heure par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -592,7 +624,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Heure par heure'!F1</f>
+              <f>'Heure par heure'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -617,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$79</f>
+              <f>'Heure par heure'!$G$2:$G$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +796,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$E$2:$E$80</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2267,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2289,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2311,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2338,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3454,7 +3510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3462,7 +3518,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3493,6 +3550,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>10-30 Le budget 2026 de l'Ét</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Vues totales</t>
         </is>
       </c>
@@ -3509,8 +3571,9 @@
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3">
-        <f>SUM(C2:E2)</f>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3">
+        <f>SUM(C2:F2)</f>
         <v/>
       </c>
     </row>
@@ -3526,8 +3589,9 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3">
-        <f>SUM(C3:E3)</f>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3">
+        <f>SUM(C3:F3)</f>
         <v/>
       </c>
     </row>
@@ -3543,8 +3607,9 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3">
-        <f>SUM(C4:E4)</f>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3">
+        <f>SUM(C4:F4)</f>
         <v/>
       </c>
     </row>
@@ -3560,8 +3625,9 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3">
-        <f>SUM(C5:E5)</f>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3">
+        <f>SUM(C5:F5)</f>
         <v/>
       </c>
     </row>
@@ -3577,8 +3643,9 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3">
-        <f>SUM(C6:E6)</f>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3">
+        <f>SUM(C6:F6)</f>
         <v/>
       </c>
     </row>
@@ -3596,8 +3663,9 @@
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3">
-        <f>SUM(C7:E7)</f>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3">
+        <f>SUM(C7:F7)</f>
         <v/>
       </c>
     </row>
@@ -3615,8 +3683,9 @@
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3">
-        <f>SUM(C8:E8)</f>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3">
+        <f>SUM(C8:F8)</f>
         <v/>
       </c>
     </row>
@@ -3634,8 +3703,9 @@
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3">
-        <f>SUM(C9:E9)</f>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3">
+        <f>SUM(C9:F9)</f>
         <v/>
       </c>
     </row>
@@ -3653,8 +3723,9 @@
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3">
-        <f>SUM(C10:E10)</f>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3">
+        <f>SUM(C10:F10)</f>
         <v/>
       </c>
     </row>
@@ -3672,8 +3743,9 @@
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3">
-        <f>SUM(C11:E11)</f>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3">
+        <f>SUM(C11:F11)</f>
         <v/>
       </c>
     </row>
@@ -3691,8 +3763,9 @@
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3">
-        <f>SUM(C12:E12)</f>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3">
+        <f>SUM(C12:F12)</f>
         <v/>
       </c>
     </row>
@@ -3710,8 +3783,9 @@
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3">
-        <f>SUM(C13:E13)</f>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3">
+        <f>SUM(C13:F13)</f>
         <v/>
       </c>
     </row>
@@ -3729,8 +3803,9 @@
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3">
-        <f>SUM(C14:E14)</f>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3">
+        <f>SUM(C14:F14)</f>
         <v/>
       </c>
     </row>
@@ -3748,8 +3823,9 @@
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3">
-        <f>SUM(C15:E15)</f>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3">
+        <f>SUM(C15:F15)</f>
         <v/>
       </c>
     </row>
@@ -3767,8 +3843,9 @@
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3">
-        <f>SUM(C16:E16)</f>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3">
+        <f>SUM(C16:F16)</f>
         <v/>
       </c>
     </row>
@@ -3786,8 +3863,9 @@
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>SUM(C17:E17)</f>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3">
+        <f>SUM(C17:F17)</f>
         <v/>
       </c>
     </row>
@@ -3805,8 +3883,9 @@
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3">
-        <f>SUM(C18:E18)</f>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3">
+        <f>SUM(C18:F18)</f>
         <v/>
       </c>
     </row>
@@ -3824,8 +3903,9 @@
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3">
-        <f>SUM(C19:E19)</f>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3">
+        <f>SUM(C19:F19)</f>
         <v/>
       </c>
     </row>
@@ -3843,8 +3923,9 @@
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3">
-        <f>SUM(C20:E20)</f>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3">
+        <f>SUM(C20:F20)</f>
         <v/>
       </c>
     </row>
@@ -3862,8 +3943,9 @@
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3">
-        <f>SUM(C21:E21)</f>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3">
+        <f>SUM(C21:F21)</f>
         <v/>
       </c>
     </row>
@@ -3881,8 +3963,9 @@
       </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3">
-        <f>SUM(C22:E22)</f>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3">
+        <f>SUM(C22:F22)</f>
         <v/>
       </c>
     </row>
@@ -3900,8 +3983,9 @@
       </c>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3">
-        <f>SUM(C23:E23)</f>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3">
+        <f>SUM(C23:F23)</f>
         <v/>
       </c>
     </row>
@@ -3919,8 +4003,9 @@
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3">
-        <f>SUM(C24:E24)</f>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3">
+        <f>SUM(C24:F24)</f>
         <v/>
       </c>
     </row>
@@ -3938,8 +4023,9 @@
       </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3">
-        <f>SUM(C25:E25)</f>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3">
+        <f>SUM(C25:F25)</f>
         <v/>
       </c>
     </row>
@@ -3957,8 +4043,9 @@
       </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3">
-        <f>SUM(C26:E26)</f>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3">
+        <f>SUM(C26:F26)</f>
         <v/>
       </c>
     </row>
@@ -3976,8 +4063,9 @@
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3">
-        <f>SUM(C27:E27)</f>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3">
+        <f>SUM(C27:F27)</f>
         <v/>
       </c>
     </row>
@@ -3999,8 +4087,9 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="3">
-        <f>SUM(C28:E28)</f>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3">
+        <f>SUM(C28:F28)</f>
         <v/>
       </c>
     </row>
@@ -4022,8 +4111,9 @@
       <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="3">
-        <f>SUM(C29:E29)</f>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3">
+        <f>SUM(C29:F29)</f>
         <v/>
       </c>
     </row>
@@ -4045,8 +4135,9 @@
       <c r="E30" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F30" s="3">
-        <f>SUM(C30:E30)</f>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3">
+        <f>SUM(C30:F30)</f>
         <v/>
       </c>
     </row>
@@ -4068,8 +4159,9 @@
       <c r="E31" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="F31" s="3">
-        <f>SUM(C31:E31)</f>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3">
+        <f>SUM(C31:F31)</f>
         <v/>
       </c>
     </row>
@@ -4091,8 +4183,9 @@
       <c r="E32" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="F32" s="3">
-        <f>SUM(C32:E32)</f>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3">
+        <f>SUM(C32:F32)</f>
         <v/>
       </c>
     </row>
@@ -4114,8 +4207,9 @@
       <c r="E33" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="F33" s="3">
-        <f>SUM(C33:E33)</f>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3">
+        <f>SUM(C33:F33)</f>
         <v/>
       </c>
     </row>
@@ -4137,8 +4231,9 @@
       <c r="E34" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="F34" s="3">
-        <f>SUM(C34:E34)</f>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3">
+        <f>SUM(C34:F34)</f>
         <v/>
       </c>
     </row>
@@ -4160,8 +4255,9 @@
       <c r="E35" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="F35" s="3">
-        <f>SUM(C35:E35)</f>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3">
+        <f>SUM(C35:F35)</f>
         <v/>
       </c>
     </row>
@@ -4183,8 +4279,9 @@
       <c r="E36" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="F36" s="3">
-        <f>SUM(C36:E36)</f>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3">
+        <f>SUM(C36:F36)</f>
         <v/>
       </c>
     </row>
@@ -4206,8 +4303,9 @@
       <c r="E37" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="F37" s="3">
-        <f>SUM(C37:E37)</f>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3">
+        <f>SUM(C37:F37)</f>
         <v/>
       </c>
     </row>
@@ -4229,8 +4327,9 @@
       <c r="E38" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F38" s="3">
-        <f>SUM(C38:E38)</f>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3">
+        <f>SUM(C38:F38)</f>
         <v/>
       </c>
     </row>
@@ -4252,8 +4351,9 @@
       <c r="E39" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="F39" s="3">
-        <f>SUM(C39:E39)</f>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3">
+        <f>SUM(C39:F39)</f>
         <v/>
       </c>
     </row>
@@ -4275,8 +4375,9 @@
       <c r="E40" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="F40" s="3">
-        <f>SUM(C40:E40)</f>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3">
+        <f>SUM(C40:F40)</f>
         <v/>
       </c>
     </row>
@@ -4298,8 +4399,9 @@
       <c r="E41" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="F41" s="3">
-        <f>SUM(C41:E41)</f>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3">
+        <f>SUM(C41:F41)</f>
         <v/>
       </c>
     </row>
@@ -4321,8 +4423,9 @@
       <c r="E42" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="F42" s="3">
-        <f>SUM(C42:E42)</f>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3">
+        <f>SUM(C42:F42)</f>
         <v/>
       </c>
     </row>
@@ -4344,8 +4447,9 @@
       <c r="E43" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F43" s="3">
-        <f>SUM(C43:E43)</f>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3">
+        <f>SUM(C43:F43)</f>
         <v/>
       </c>
     </row>
@@ -4367,8 +4471,9 @@
       <c r="E44" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F44" s="3">
-        <f>SUM(C44:E44)</f>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3">
+        <f>SUM(C44:F44)</f>
         <v/>
       </c>
     </row>
@@ -4390,8 +4495,9 @@
       <c r="E45" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="F45" s="3">
-        <f>SUM(C45:E45)</f>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3">
+        <f>SUM(C45:F45)</f>
         <v/>
       </c>
     </row>
@@ -4413,8 +4519,9 @@
       <c r="E46" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F46" s="3">
-        <f>SUM(C46:E46)</f>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3">
+        <f>SUM(C46:F46)</f>
         <v/>
       </c>
     </row>
@@ -4436,8 +4543,9 @@
       <c r="E47" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F47" s="3">
-        <f>SUM(C47:E47)</f>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3">
+        <f>SUM(C47:F47)</f>
         <v/>
       </c>
     </row>
@@ -4459,8 +4567,9 @@
       <c r="E48" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F48" s="3">
-        <f>SUM(C48:E48)</f>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3">
+        <f>SUM(C48:F48)</f>
         <v/>
       </c>
     </row>
@@ -4482,8 +4591,9 @@
       <c r="E49" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F49" s="3">
-        <f>SUM(C49:E49)</f>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3">
+        <f>SUM(C49:F49)</f>
         <v/>
       </c>
     </row>
@@ -4505,8 +4615,9 @@
       <c r="E50" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F50" s="3">
-        <f>SUM(C50:E50)</f>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3">
+        <f>SUM(C50:F50)</f>
         <v/>
       </c>
     </row>
@@ -4528,8 +4639,9 @@
       <c r="E51" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F51" s="3">
-        <f>SUM(C51:E51)</f>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3">
+        <f>SUM(C51:F51)</f>
         <v/>
       </c>
     </row>
@@ -4551,8 +4663,9 @@
       <c r="E52" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F52" s="3">
-        <f>SUM(C52:E52)</f>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3">
+        <f>SUM(C52:F52)</f>
         <v/>
       </c>
     </row>
@@ -4574,8 +4687,9 @@
       <c r="E53" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F53" s="3">
-        <f>SUM(C53:E53)</f>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3">
+        <f>SUM(C53:F53)</f>
         <v/>
       </c>
     </row>
@@ -4597,8 +4711,9 @@
       <c r="E54" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F54" s="3">
-        <f>SUM(C54:E54)</f>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3">
+        <f>SUM(C54:F54)</f>
         <v/>
       </c>
     </row>
@@ -4620,8 +4735,9 @@
       <c r="E55" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F55" s="3">
-        <f>SUM(C55:E55)</f>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3">
+        <f>SUM(C55:F55)</f>
         <v/>
       </c>
     </row>
@@ -4643,8 +4759,9 @@
       <c r="E56" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F56" s="3">
-        <f>SUM(C56:E56)</f>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3">
+        <f>SUM(C56:F56)</f>
         <v/>
       </c>
     </row>
@@ -4666,8 +4783,9 @@
       <c r="E57" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F57" s="3">
-        <f>SUM(C57:E57)</f>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3">
+        <f>SUM(C57:F57)</f>
         <v/>
       </c>
     </row>
@@ -4689,8 +4807,9 @@
       <c r="E58" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F58" s="3">
-        <f>SUM(C58:E58)</f>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3">
+        <f>SUM(C58:F58)</f>
         <v/>
       </c>
     </row>
@@ -4712,8 +4831,9 @@
       <c r="E59" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F59" s="3">
-        <f>SUM(C59:E59)</f>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3">
+        <f>SUM(C59:F59)</f>
         <v/>
       </c>
     </row>
@@ -4735,8 +4855,9 @@
       <c r="E60" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F60" s="3">
-        <f>SUM(C60:E60)</f>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3">
+        <f>SUM(C60:F60)</f>
         <v/>
       </c>
     </row>
@@ -4758,8 +4879,9 @@
       <c r="E61" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F61" s="3">
-        <f>SUM(C61:E61)</f>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3">
+        <f>SUM(C61:F61)</f>
         <v/>
       </c>
     </row>
@@ -4781,8 +4903,9 @@
       <c r="E62" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F62" s="3">
-        <f>SUM(C62:E62)</f>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3">
+        <f>SUM(C62:F62)</f>
         <v/>
       </c>
     </row>
@@ -4804,8 +4927,9 @@
       <c r="E63" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F63" s="3">
-        <f>SUM(C63:E63)</f>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3">
+        <f>SUM(C63:F63)</f>
         <v/>
       </c>
     </row>
@@ -4827,8 +4951,9 @@
       <c r="E64" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F64" s="3">
-        <f>SUM(C64:E64)</f>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3">
+        <f>SUM(C64:F64)</f>
         <v/>
       </c>
     </row>
@@ -4850,8 +4975,9 @@
       <c r="E65" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F65" s="3">
-        <f>SUM(C65:E65)</f>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3">
+        <f>SUM(C65:F65)</f>
         <v/>
       </c>
     </row>
@@ -4873,8 +4999,9 @@
       <c r="E66" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F66" s="3">
-        <f>SUM(C66:E66)</f>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3">
+        <f>SUM(C66:F66)</f>
         <v/>
       </c>
     </row>
@@ -4896,8 +5023,9 @@
       <c r="E67" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F67" s="3">
-        <f>SUM(C67:E67)</f>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3">
+        <f>SUM(C67:F67)</f>
         <v/>
       </c>
     </row>
@@ -4919,8 +5047,9 @@
       <c r="E68" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F68" s="3">
-        <f>SUM(C68:E68)</f>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3">
+        <f>SUM(C68:F68)</f>
         <v/>
       </c>
     </row>
@@ -4942,8 +5071,9 @@
       <c r="E69" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F69" s="3">
-        <f>SUM(C69:E69)</f>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3">
+        <f>SUM(C69:F69)</f>
         <v/>
       </c>
     </row>
@@ -4965,8 +5095,9 @@
       <c r="E70" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F70" s="3">
-        <f>SUM(C70:E70)</f>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3">
+        <f>SUM(C70:F70)</f>
         <v/>
       </c>
     </row>
@@ -4988,8 +5119,9 @@
       <c r="E71" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F71" s="3">
-        <f>SUM(C71:E71)</f>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3">
+        <f>SUM(C71:F71)</f>
         <v/>
       </c>
     </row>
@@ -5011,8 +5143,9 @@
       <c r="E72" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F72" s="3">
-        <f>SUM(C72:E72)</f>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3">
+        <f>SUM(C72:F72)</f>
         <v/>
       </c>
     </row>
@@ -5034,8 +5167,9 @@
       <c r="E73" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F73" s="3">
-        <f>SUM(C73:E73)</f>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3">
+        <f>SUM(C73:F73)</f>
         <v/>
       </c>
     </row>
@@ -5057,8 +5191,9 @@
       <c r="E74" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F74" s="3">
-        <f>SUM(C74:E74)</f>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3">
+        <f>SUM(C74:F74)</f>
         <v/>
       </c>
     </row>
@@ -5080,8 +5215,9 @@
       <c r="E75" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F75" s="3">
-        <f>SUM(C75:E75)</f>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3">
+        <f>SUM(C75:F75)</f>
         <v/>
       </c>
     </row>
@@ -5103,8 +5239,9 @@
       <c r="E76" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F76" s="3">
-        <f>SUM(C76:E76)</f>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3">
+        <f>SUM(C76:F76)</f>
         <v/>
       </c>
     </row>
@@ -5126,8 +5263,9 @@
       <c r="E77" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F77" s="3">
-        <f>SUM(C77:E77)</f>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3">
+        <f>SUM(C77:F77)</f>
         <v/>
       </c>
     </row>
@@ -5149,8 +5287,9 @@
       <c r="E78" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F78" s="3">
-        <f>SUM(C78:E78)</f>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3">
+        <f>SUM(C78:F78)</f>
         <v/>
       </c>
     </row>
@@ -5172,8 +5311,35 @@
       <c r="E79" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F79" s="3">
-        <f>SUM(C79:E79)</f>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3">
+        <f>SUM(C79:F79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:00</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
+        <f>SUM(C80:F80)</f>
         <v/>
       </c>
     </row>
@@ -5189,14 +5355,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -5222,6 +5389,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>10-30 Le budget 2026 de l'Ét</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Total de l'heure</t>
         </is>
       </c>
@@ -5234,8 +5406,9 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3">
-        <f>SUM(B2:D2)</f>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3">
+        <f>SUM(B2:E2)</f>
         <v/>
       </c>
     </row>
@@ -5257,7 +5430,11 @@
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>SUM(B3:D3)</f>
+        <f>IF('Heure par heure'!F3="","",'Heure par heure'!F3-N('Heure par heure'!F2))</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>SUM(B3:E3)</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +5456,11 @@
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>SUM(B4:D4)</f>
+        <f>IF('Heure par heure'!F4="","",'Heure par heure'!F4-N('Heure par heure'!F3))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>SUM(B4:E4)</f>
         <v/>
       </c>
     </row>
@@ -5301,7 +5482,11 @@
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>SUM(B5:D5)</f>
+        <f>IF('Heure par heure'!F5="","",'Heure par heure'!F5-N('Heure par heure'!F4))</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>SUM(B5:E5)</f>
         <v/>
       </c>
     </row>
@@ -5323,7 +5508,11 @@
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>SUM(B6:D6)</f>
+        <f>IF('Heure par heure'!F6="","",'Heure par heure'!F6-N('Heure par heure'!F5))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>SUM(B6:E6)</f>
         <v/>
       </c>
     </row>
@@ -5345,7 +5534,11 @@
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>SUM(B7:D7)</f>
+        <f>IF('Heure par heure'!F7="","",'Heure par heure'!F7-N('Heure par heure'!F6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>SUM(B7:E7)</f>
         <v/>
       </c>
     </row>
@@ -5367,7 +5560,11 @@
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>SUM(B8:D8)</f>
+        <f>IF('Heure par heure'!F8="","",'Heure par heure'!F8-N('Heure par heure'!F7))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>SUM(B8:E8)</f>
         <v/>
       </c>
     </row>
@@ -5389,7 +5586,11 @@
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>SUM(B9:D9)</f>
+        <f>IF('Heure par heure'!F9="","",'Heure par heure'!F9-N('Heure par heure'!F8))</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>SUM(B9:E9)</f>
         <v/>
       </c>
     </row>
@@ -5411,7 +5612,11 @@
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>SUM(B10:D10)</f>
+        <f>IF('Heure par heure'!F10="","",'Heure par heure'!F10-N('Heure par heure'!F9))</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>SUM(B10:E10)</f>
         <v/>
       </c>
     </row>
@@ -5433,7 +5638,11 @@
         <v/>
       </c>
       <c r="E11" s="3">
-        <f>SUM(B11:D11)</f>
+        <f>IF('Heure par heure'!F11="","",'Heure par heure'!F11-N('Heure par heure'!F10))</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>SUM(B11:E11)</f>
         <v/>
       </c>
     </row>
@@ -5455,7 +5664,11 @@
         <v/>
       </c>
       <c r="E12" s="3">
-        <f>SUM(B12:D12)</f>
+        <f>IF('Heure par heure'!F12="","",'Heure par heure'!F12-N('Heure par heure'!F11))</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>SUM(B12:E12)</f>
         <v/>
       </c>
     </row>
@@ -5477,7 +5690,11 @@
         <v/>
       </c>
       <c r="E13" s="3">
-        <f>SUM(B13:D13)</f>
+        <f>IF('Heure par heure'!F13="","",'Heure par heure'!F13-N('Heure par heure'!F12))</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>SUM(B13:E13)</f>
         <v/>
       </c>
     </row>
@@ -5499,7 +5716,11 @@
         <v/>
       </c>
       <c r="E14" s="3">
-        <f>SUM(B14:D14)</f>
+        <f>IF('Heure par heure'!F14="","",'Heure par heure'!F14-N('Heure par heure'!F13))</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>SUM(B14:E14)</f>
         <v/>
       </c>
     </row>
@@ -5521,7 +5742,11 @@
         <v/>
       </c>
       <c r="E15" s="3">
-        <f>SUM(B15:D15)</f>
+        <f>IF('Heure par heure'!F15="","",'Heure par heure'!F15-N('Heure par heure'!F14))</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>SUM(B15:E15)</f>
         <v/>
       </c>
     </row>
@@ -5543,7 +5768,11 @@
         <v/>
       </c>
       <c r="E16" s="3">
-        <f>SUM(B16:D16)</f>
+        <f>IF('Heure par heure'!F16="","",'Heure par heure'!F16-N('Heure par heure'!F15))</f>
+        <v/>
+      </c>
+      <c r="F16" s="3">
+        <f>SUM(B16:E16)</f>
         <v/>
       </c>
     </row>
@@ -5565,7 +5794,11 @@
         <v/>
       </c>
       <c r="E17" s="3">
-        <f>SUM(B17:D17)</f>
+        <f>IF('Heure par heure'!F17="","",'Heure par heure'!F17-N('Heure par heure'!F16))</f>
+        <v/>
+      </c>
+      <c r="F17" s="3">
+        <f>SUM(B17:E17)</f>
         <v/>
       </c>
     </row>
@@ -5587,7 +5820,11 @@
         <v/>
       </c>
       <c r="E18" s="3">
-        <f>SUM(B18:D18)</f>
+        <f>IF('Heure par heure'!F18="","",'Heure par heure'!F18-N('Heure par heure'!F17))</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>SUM(B18:E18)</f>
         <v/>
       </c>
     </row>
@@ -5609,7 +5846,11 @@
         <v/>
       </c>
       <c r="E19" s="3">
-        <f>SUM(B19:D19)</f>
+        <f>IF('Heure par heure'!F19="","",'Heure par heure'!F19-N('Heure par heure'!F18))</f>
+        <v/>
+      </c>
+      <c r="F19" s="3">
+        <f>SUM(B19:E19)</f>
         <v/>
       </c>
     </row>
@@ -5631,7 +5872,11 @@
         <v/>
       </c>
       <c r="E20" s="3">
-        <f>SUM(B20:D20)</f>
+        <f>IF('Heure par heure'!F20="","",'Heure par heure'!F20-N('Heure par heure'!F19))</f>
+        <v/>
+      </c>
+      <c r="F20" s="3">
+        <f>SUM(B20:E20)</f>
         <v/>
       </c>
     </row>
@@ -5653,7 +5898,11 @@
         <v/>
       </c>
       <c r="E21" s="3">
-        <f>SUM(B21:D21)</f>
+        <f>IF('Heure par heure'!F21="","",'Heure par heure'!F21-N('Heure par heure'!F20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>SUM(B21:E21)</f>
         <v/>
       </c>
     </row>
@@ -5675,7 +5924,11 @@
         <v/>
       </c>
       <c r="E22" s="3">
-        <f>SUM(B22:D22)</f>
+        <f>IF('Heure par heure'!F22="","",'Heure par heure'!F22-N('Heure par heure'!F21))</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>SUM(B22:E22)</f>
         <v/>
       </c>
     </row>
@@ -5697,7 +5950,11 @@
         <v/>
       </c>
       <c r="E23" s="3">
-        <f>SUM(B23:D23)</f>
+        <f>IF('Heure par heure'!F23="","",'Heure par heure'!F23-N('Heure par heure'!F22))</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>SUM(B23:E23)</f>
         <v/>
       </c>
     </row>
@@ -5719,7 +5976,11 @@
         <v/>
       </c>
       <c r="E24" s="3">
-        <f>SUM(B24:D24)</f>
+        <f>IF('Heure par heure'!F24="","",'Heure par heure'!F24-N('Heure par heure'!F23))</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>SUM(B24:E24)</f>
         <v/>
       </c>
     </row>
@@ -5741,7 +6002,11 @@
         <v/>
       </c>
       <c r="E25" s="3">
-        <f>SUM(B25:D25)</f>
+        <f>IF('Heure par heure'!F25="","",'Heure par heure'!F25-N('Heure par heure'!F24))</f>
+        <v/>
+      </c>
+      <c r="F25" s="3">
+        <f>SUM(B25:E25)</f>
         <v/>
       </c>
     </row>
@@ -5763,7 +6028,11 @@
         <v/>
       </c>
       <c r="E26" s="3">
-        <f>SUM(B26:D26)</f>
+        <f>IF('Heure par heure'!F26="","",'Heure par heure'!F26-N('Heure par heure'!F25))</f>
+        <v/>
+      </c>
+      <c r="F26" s="3">
+        <f>SUM(B26:E26)</f>
         <v/>
       </c>
     </row>
@@ -5785,7 +6054,11 @@
         <v/>
       </c>
       <c r="E27" s="3">
-        <f>SUM(B27:D27)</f>
+        <f>IF('Heure par heure'!F27="","",'Heure par heure'!F27-N('Heure par heure'!F26))</f>
+        <v/>
+      </c>
+      <c r="F27" s="3">
+        <f>SUM(B27:E27)</f>
         <v/>
       </c>
     </row>
@@ -5807,7 +6080,11 @@
         <v/>
       </c>
       <c r="E28" s="3">
-        <f>SUM(B28:D28)</f>
+        <f>IF('Heure par heure'!F28="","",'Heure par heure'!F28-N('Heure par heure'!F27))</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>SUM(B28:E28)</f>
         <v/>
       </c>
     </row>
@@ -5829,7 +6106,11 @@
         <v/>
       </c>
       <c r="E29" s="3">
-        <f>SUM(B29:D29)</f>
+        <f>IF('Heure par heure'!F29="","",'Heure par heure'!F29-N('Heure par heure'!F28))</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>SUM(B29:E29)</f>
         <v/>
       </c>
     </row>
@@ -5851,7 +6132,11 @@
         <v/>
       </c>
       <c r="E30" s="3">
-        <f>SUM(B30:D30)</f>
+        <f>IF('Heure par heure'!F30="","",'Heure par heure'!F30-N('Heure par heure'!F29))</f>
+        <v/>
+      </c>
+      <c r="F30" s="3">
+        <f>SUM(B30:E30)</f>
         <v/>
       </c>
     </row>
@@ -5873,7 +6158,11 @@
         <v/>
       </c>
       <c r="E31" s="3">
-        <f>SUM(B31:D31)</f>
+        <f>IF('Heure par heure'!F31="","",'Heure par heure'!F31-N('Heure par heure'!F30))</f>
+        <v/>
+      </c>
+      <c r="F31" s="3">
+        <f>SUM(B31:E31)</f>
         <v/>
       </c>
     </row>
@@ -5895,7 +6184,11 @@
         <v/>
       </c>
       <c r="E32" s="3">
-        <f>SUM(B32:D32)</f>
+        <f>IF('Heure par heure'!F32="","",'Heure par heure'!F32-N('Heure par heure'!F31))</f>
+        <v/>
+      </c>
+      <c r="F32" s="3">
+        <f>SUM(B32:E32)</f>
         <v/>
       </c>
     </row>
@@ -5917,7 +6210,11 @@
         <v/>
       </c>
       <c r="E33" s="3">
-        <f>SUM(B33:D33)</f>
+        <f>IF('Heure par heure'!F33="","",'Heure par heure'!F33-N('Heure par heure'!F32))</f>
+        <v/>
+      </c>
+      <c r="F33" s="3">
+        <f>SUM(B33:E33)</f>
         <v/>
       </c>
     </row>
@@ -5939,7 +6236,11 @@
         <v/>
       </c>
       <c r="E34" s="3">
-        <f>SUM(B34:D34)</f>
+        <f>IF('Heure par heure'!F34="","",'Heure par heure'!F34-N('Heure par heure'!F33))</f>
+        <v/>
+      </c>
+      <c r="F34" s="3">
+        <f>SUM(B34:E34)</f>
         <v/>
       </c>
     </row>
@@ -5961,7 +6262,11 @@
         <v/>
       </c>
       <c r="E35" s="3">
-        <f>SUM(B35:D35)</f>
+        <f>IF('Heure par heure'!F35="","",'Heure par heure'!F35-N('Heure par heure'!F34))</f>
+        <v/>
+      </c>
+      <c r="F35" s="3">
+        <f>SUM(B35:E35)</f>
         <v/>
       </c>
     </row>
@@ -5983,7 +6288,11 @@
         <v/>
       </c>
       <c r="E36" s="3">
-        <f>SUM(B36:D36)</f>
+        <f>IF('Heure par heure'!F36="","",'Heure par heure'!F36-N('Heure par heure'!F35))</f>
+        <v/>
+      </c>
+      <c r="F36" s="3">
+        <f>SUM(B36:E36)</f>
         <v/>
       </c>
     </row>
@@ -6005,7 +6314,11 @@
         <v/>
       </c>
       <c r="E37" s="3">
-        <f>SUM(B37:D37)</f>
+        <f>IF('Heure par heure'!F37="","",'Heure par heure'!F37-N('Heure par heure'!F36))</f>
+        <v/>
+      </c>
+      <c r="F37" s="3">
+        <f>SUM(B37:E37)</f>
         <v/>
       </c>
     </row>
@@ -6027,7 +6340,11 @@
         <v/>
       </c>
       <c r="E38" s="3">
-        <f>SUM(B38:D38)</f>
+        <f>IF('Heure par heure'!F38="","",'Heure par heure'!F38-N('Heure par heure'!F37))</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>SUM(B38:E38)</f>
         <v/>
       </c>
     </row>
@@ -6049,7 +6366,11 @@
         <v/>
       </c>
       <c r="E39" s="3">
-        <f>SUM(B39:D39)</f>
+        <f>IF('Heure par heure'!F39="","",'Heure par heure'!F39-N('Heure par heure'!F38))</f>
+        <v/>
+      </c>
+      <c r="F39" s="3">
+        <f>SUM(B39:E39)</f>
         <v/>
       </c>
     </row>
@@ -6071,7 +6392,11 @@
         <v/>
       </c>
       <c r="E40" s="3">
-        <f>SUM(B40:D40)</f>
+        <f>IF('Heure par heure'!F40="","",'Heure par heure'!F40-N('Heure par heure'!F39))</f>
+        <v/>
+      </c>
+      <c r="F40" s="3">
+        <f>SUM(B40:E40)</f>
         <v/>
       </c>
     </row>
@@ -6093,7 +6418,11 @@
         <v/>
       </c>
       <c r="E41" s="3">
-        <f>SUM(B41:D41)</f>
+        <f>IF('Heure par heure'!F41="","",'Heure par heure'!F41-N('Heure par heure'!F40))</f>
+        <v/>
+      </c>
+      <c r="F41" s="3">
+        <f>SUM(B41:E41)</f>
         <v/>
       </c>
     </row>
@@ -6115,7 +6444,11 @@
         <v/>
       </c>
       <c r="E42" s="3">
-        <f>SUM(B42:D42)</f>
+        <f>IF('Heure par heure'!F42="","",'Heure par heure'!F42-N('Heure par heure'!F41))</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>SUM(B42:E42)</f>
         <v/>
       </c>
     </row>
@@ -6137,7 +6470,11 @@
         <v/>
       </c>
       <c r="E43" s="3">
-        <f>SUM(B43:D43)</f>
+        <f>IF('Heure par heure'!F43="","",'Heure par heure'!F43-N('Heure par heure'!F42))</f>
+        <v/>
+      </c>
+      <c r="F43" s="3">
+        <f>SUM(B43:E43)</f>
         <v/>
       </c>
     </row>
@@ -6159,7 +6496,11 @@
         <v/>
       </c>
       <c r="E44" s="3">
-        <f>SUM(B44:D44)</f>
+        <f>IF('Heure par heure'!F44="","",'Heure par heure'!F44-N('Heure par heure'!F43))</f>
+        <v/>
+      </c>
+      <c r="F44" s="3">
+        <f>SUM(B44:E44)</f>
         <v/>
       </c>
     </row>
@@ -6181,7 +6522,11 @@
         <v/>
       </c>
       <c r="E45" s="3">
-        <f>SUM(B45:D45)</f>
+        <f>IF('Heure par heure'!F45="","",'Heure par heure'!F45-N('Heure par heure'!F44))</f>
+        <v/>
+      </c>
+      <c r="F45" s="3">
+        <f>SUM(B45:E45)</f>
         <v/>
       </c>
     </row>
@@ -6203,7 +6548,11 @@
         <v/>
       </c>
       <c r="E46" s="3">
-        <f>SUM(B46:D46)</f>
+        <f>IF('Heure par heure'!F46="","",'Heure par heure'!F46-N('Heure par heure'!F45))</f>
+        <v/>
+      </c>
+      <c r="F46" s="3">
+        <f>SUM(B46:E46)</f>
         <v/>
       </c>
     </row>
@@ -6225,7 +6574,11 @@
         <v/>
       </c>
       <c r="E47" s="3">
-        <f>SUM(B47:D47)</f>
+        <f>IF('Heure par heure'!F47="","",'Heure par heure'!F47-N('Heure par heure'!F46))</f>
+        <v/>
+      </c>
+      <c r="F47" s="3">
+        <f>SUM(B47:E47)</f>
         <v/>
       </c>
     </row>
@@ -6247,7 +6600,11 @@
         <v/>
       </c>
       <c r="E48" s="3">
-        <f>SUM(B48:D48)</f>
+        <f>IF('Heure par heure'!F48="","",'Heure par heure'!F48-N('Heure par heure'!F47))</f>
+        <v/>
+      </c>
+      <c r="F48" s="3">
+        <f>SUM(B48:E48)</f>
         <v/>
       </c>
     </row>
@@ -6269,7 +6626,11 @@
         <v/>
       </c>
       <c r="E49" s="3">
-        <f>SUM(B49:D49)</f>
+        <f>IF('Heure par heure'!F49="","",'Heure par heure'!F49-N('Heure par heure'!F48))</f>
+        <v/>
+      </c>
+      <c r="F49" s="3">
+        <f>SUM(B49:E49)</f>
         <v/>
       </c>
     </row>
@@ -6291,7 +6652,11 @@
         <v/>
       </c>
       <c r="E50" s="3">
-        <f>SUM(B50:D50)</f>
+        <f>IF('Heure par heure'!F50="","",'Heure par heure'!F50-N('Heure par heure'!F49))</f>
+        <v/>
+      </c>
+      <c r="F50" s="3">
+        <f>SUM(B50:E50)</f>
         <v/>
       </c>
     </row>
@@ -6313,7 +6678,11 @@
         <v/>
       </c>
       <c r="E51" s="3">
-        <f>SUM(B51:D51)</f>
+        <f>IF('Heure par heure'!F51="","",'Heure par heure'!F51-N('Heure par heure'!F50))</f>
+        <v/>
+      </c>
+      <c r="F51" s="3">
+        <f>SUM(B51:E51)</f>
         <v/>
       </c>
     </row>
@@ -6335,7 +6704,11 @@
         <v/>
       </c>
       <c r="E52" s="3">
-        <f>SUM(B52:D52)</f>
+        <f>IF('Heure par heure'!F52="","",'Heure par heure'!F52-N('Heure par heure'!F51))</f>
+        <v/>
+      </c>
+      <c r="F52" s="3">
+        <f>SUM(B52:E52)</f>
         <v/>
       </c>
     </row>
@@ -6357,7 +6730,11 @@
         <v/>
       </c>
       <c r="E53" s="3">
-        <f>SUM(B53:D53)</f>
+        <f>IF('Heure par heure'!F53="","",'Heure par heure'!F53-N('Heure par heure'!F52))</f>
+        <v/>
+      </c>
+      <c r="F53" s="3">
+        <f>SUM(B53:E53)</f>
         <v/>
       </c>
     </row>
@@ -6379,7 +6756,11 @@
         <v/>
       </c>
       <c r="E54" s="3">
-        <f>SUM(B54:D54)</f>
+        <f>IF('Heure par heure'!F54="","",'Heure par heure'!F54-N('Heure par heure'!F53))</f>
+        <v/>
+      </c>
+      <c r="F54" s="3">
+        <f>SUM(B54:E54)</f>
         <v/>
       </c>
     </row>
@@ -6401,7 +6782,11 @@
         <v/>
       </c>
       <c r="E55" s="3">
-        <f>SUM(B55:D55)</f>
+        <f>IF('Heure par heure'!F55="","",'Heure par heure'!F55-N('Heure par heure'!F54))</f>
+        <v/>
+      </c>
+      <c r="F55" s="3">
+        <f>SUM(B55:E55)</f>
         <v/>
       </c>
     </row>
@@ -6423,7 +6808,11 @@
         <v/>
       </c>
       <c r="E56" s="3">
-        <f>SUM(B56:D56)</f>
+        <f>IF('Heure par heure'!F56="","",'Heure par heure'!F56-N('Heure par heure'!F55))</f>
+        <v/>
+      </c>
+      <c r="F56" s="3">
+        <f>SUM(B56:E56)</f>
         <v/>
       </c>
     </row>
@@ -6445,7 +6834,11 @@
         <v/>
       </c>
       <c r="E57" s="3">
-        <f>SUM(B57:D57)</f>
+        <f>IF('Heure par heure'!F57="","",'Heure par heure'!F57-N('Heure par heure'!F56))</f>
+        <v/>
+      </c>
+      <c r="F57" s="3">
+        <f>SUM(B57:E57)</f>
         <v/>
       </c>
     </row>
@@ -6467,7 +6860,11 @@
         <v/>
       </c>
       <c r="E58" s="3">
-        <f>SUM(B58:D58)</f>
+        <f>IF('Heure par heure'!F58="","",'Heure par heure'!F58-N('Heure par heure'!F57))</f>
+        <v/>
+      </c>
+      <c r="F58" s="3">
+        <f>SUM(B58:E58)</f>
         <v/>
       </c>
     </row>
@@ -6489,7 +6886,11 @@
         <v/>
       </c>
       <c r="E59" s="3">
-        <f>SUM(B59:D59)</f>
+        <f>IF('Heure par heure'!F59="","",'Heure par heure'!F59-N('Heure par heure'!F58))</f>
+        <v/>
+      </c>
+      <c r="F59" s="3">
+        <f>SUM(B59:E59)</f>
         <v/>
       </c>
     </row>
@@ -6511,7 +6912,11 @@
         <v/>
       </c>
       <c r="E60" s="3">
-        <f>SUM(B60:D60)</f>
+        <f>IF('Heure par heure'!F60="","",'Heure par heure'!F60-N('Heure par heure'!F59))</f>
+        <v/>
+      </c>
+      <c r="F60" s="3">
+        <f>SUM(B60:E60)</f>
         <v/>
       </c>
     </row>
@@ -6533,7 +6938,11 @@
         <v/>
       </c>
       <c r="E61" s="3">
-        <f>SUM(B61:D61)</f>
+        <f>IF('Heure par heure'!F61="","",'Heure par heure'!F61-N('Heure par heure'!F60))</f>
+        <v/>
+      </c>
+      <c r="F61" s="3">
+        <f>SUM(B61:E61)</f>
         <v/>
       </c>
     </row>
@@ -6555,7 +6964,11 @@
         <v/>
       </c>
       <c r="E62" s="3">
-        <f>SUM(B62:D62)</f>
+        <f>IF('Heure par heure'!F62="","",'Heure par heure'!F62-N('Heure par heure'!F61))</f>
+        <v/>
+      </c>
+      <c r="F62" s="3">
+        <f>SUM(B62:E62)</f>
         <v/>
       </c>
     </row>
@@ -6577,7 +6990,11 @@
         <v/>
       </c>
       <c r="E63" s="3">
-        <f>SUM(B63:D63)</f>
+        <f>IF('Heure par heure'!F63="","",'Heure par heure'!F63-N('Heure par heure'!F62))</f>
+        <v/>
+      </c>
+      <c r="F63" s="3">
+        <f>SUM(B63:E63)</f>
         <v/>
       </c>
     </row>
@@ -6599,7 +7016,11 @@
         <v/>
       </c>
       <c r="E64" s="3">
-        <f>SUM(B64:D64)</f>
+        <f>IF('Heure par heure'!F64="","",'Heure par heure'!F64-N('Heure par heure'!F63))</f>
+        <v/>
+      </c>
+      <c r="F64" s="3">
+        <f>SUM(B64:E64)</f>
         <v/>
       </c>
     </row>
@@ -6621,7 +7042,11 @@
         <v/>
       </c>
       <c r="E65" s="3">
-        <f>SUM(B65:D65)</f>
+        <f>IF('Heure par heure'!F65="","",'Heure par heure'!F65-N('Heure par heure'!F64))</f>
+        <v/>
+      </c>
+      <c r="F65" s="3">
+        <f>SUM(B65:E65)</f>
         <v/>
       </c>
     </row>
@@ -6643,7 +7068,11 @@
         <v/>
       </c>
       <c r="E66" s="3">
-        <f>SUM(B66:D66)</f>
+        <f>IF('Heure par heure'!F66="","",'Heure par heure'!F66-N('Heure par heure'!F65))</f>
+        <v/>
+      </c>
+      <c r="F66" s="3">
+        <f>SUM(B66:E66)</f>
         <v/>
       </c>
     </row>
@@ -6665,7 +7094,11 @@
         <v/>
       </c>
       <c r="E67" s="3">
-        <f>SUM(B67:D67)</f>
+        <f>IF('Heure par heure'!F67="","",'Heure par heure'!F67-N('Heure par heure'!F66))</f>
+        <v/>
+      </c>
+      <c r="F67" s="3">
+        <f>SUM(B67:E67)</f>
         <v/>
       </c>
     </row>
@@ -6687,7 +7120,11 @@
         <v/>
       </c>
       <c r="E68" s="3">
-        <f>SUM(B68:D68)</f>
+        <f>IF('Heure par heure'!F68="","",'Heure par heure'!F68-N('Heure par heure'!F67))</f>
+        <v/>
+      </c>
+      <c r="F68" s="3">
+        <f>SUM(B68:E68)</f>
         <v/>
       </c>
     </row>
@@ -6709,7 +7146,11 @@
         <v/>
       </c>
       <c r="E69" s="3">
-        <f>SUM(B69:D69)</f>
+        <f>IF('Heure par heure'!F69="","",'Heure par heure'!F69-N('Heure par heure'!F68))</f>
+        <v/>
+      </c>
+      <c r="F69" s="3">
+        <f>SUM(B69:E69)</f>
         <v/>
       </c>
     </row>
@@ -6731,7 +7172,11 @@
         <v/>
       </c>
       <c r="E70" s="3">
-        <f>SUM(B70:D70)</f>
+        <f>IF('Heure par heure'!F70="","",'Heure par heure'!F70-N('Heure par heure'!F69))</f>
+        <v/>
+      </c>
+      <c r="F70" s="3">
+        <f>SUM(B70:E70)</f>
         <v/>
       </c>
     </row>
@@ -6753,7 +7198,11 @@
         <v/>
       </c>
       <c r="E71" s="3">
-        <f>SUM(B71:D71)</f>
+        <f>IF('Heure par heure'!F71="","",'Heure par heure'!F71-N('Heure par heure'!F70))</f>
+        <v/>
+      </c>
+      <c r="F71" s="3">
+        <f>SUM(B71:E71)</f>
         <v/>
       </c>
     </row>
@@ -6775,7 +7224,11 @@
         <v/>
       </c>
       <c r="E72" s="3">
-        <f>SUM(B72:D72)</f>
+        <f>IF('Heure par heure'!F72="","",'Heure par heure'!F72-N('Heure par heure'!F71))</f>
+        <v/>
+      </c>
+      <c r="F72" s="3">
+        <f>SUM(B72:E72)</f>
         <v/>
       </c>
     </row>
@@ -6797,7 +7250,11 @@
         <v/>
       </c>
       <c r="E73" s="3">
-        <f>SUM(B73:D73)</f>
+        <f>IF('Heure par heure'!F73="","",'Heure par heure'!F73-N('Heure par heure'!F72))</f>
+        <v/>
+      </c>
+      <c r="F73" s="3">
+        <f>SUM(B73:E73)</f>
         <v/>
       </c>
     </row>
@@ -6819,7 +7276,11 @@
         <v/>
       </c>
       <c r="E74" s="3">
-        <f>SUM(B74:D74)</f>
+        <f>IF('Heure par heure'!F74="","",'Heure par heure'!F74-N('Heure par heure'!F73))</f>
+        <v/>
+      </c>
+      <c r="F74" s="3">
+        <f>SUM(B74:E74)</f>
         <v/>
       </c>
     </row>
@@ -6841,7 +7302,11 @@
         <v/>
       </c>
       <c r="E75" s="3">
-        <f>SUM(B75:D75)</f>
+        <f>IF('Heure par heure'!F75="","",'Heure par heure'!F75-N('Heure par heure'!F74))</f>
+        <v/>
+      </c>
+      <c r="F75" s="3">
+        <f>SUM(B75:E75)</f>
         <v/>
       </c>
     </row>
@@ -6863,7 +7328,11 @@
         <v/>
       </c>
       <c r="E76" s="3">
-        <f>SUM(B76:D76)</f>
+        <f>IF('Heure par heure'!F76="","",'Heure par heure'!F76-N('Heure par heure'!F75))</f>
+        <v/>
+      </c>
+      <c r="F76" s="3">
+        <f>SUM(B76:E76)</f>
         <v/>
       </c>
     </row>
@@ -6885,7 +7354,11 @@
         <v/>
       </c>
       <c r="E77" s="3">
-        <f>SUM(B77:D77)</f>
+        <f>IF('Heure par heure'!F77="","",'Heure par heure'!F77-N('Heure par heure'!F76))</f>
+        <v/>
+      </c>
+      <c r="F77" s="3">
+        <f>SUM(B77:E77)</f>
         <v/>
       </c>
     </row>
@@ -6907,7 +7380,11 @@
         <v/>
       </c>
       <c r="E78" s="3">
-        <f>SUM(B78:D78)</f>
+        <f>IF('Heure par heure'!F78="","",'Heure par heure'!F78-N('Heure par heure'!F77))</f>
+        <v/>
+      </c>
+      <c r="F78" s="3">
+        <f>SUM(B78:E78)</f>
         <v/>
       </c>
     </row>
@@ -6929,7 +7406,37 @@
         <v/>
       </c>
       <c r="E79" s="3">
-        <f>SUM(B79:D79)</f>
+        <f>IF('Heure par heure'!F79="","",'Heure par heure'!F79-N('Heure par heure'!F78))</f>
+        <v/>
+      </c>
+      <c r="F79" s="3">
+        <f>SUM(B79:E79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <f>'Heure par heure'!A80</f>
+        <v/>
+      </c>
+      <c r="B80" s="3">
+        <f>IF('Heure par heure'!C80="","",'Heure par heure'!C80-N('Heure par heure'!C79))</f>
+        <v/>
+      </c>
+      <c r="C80" s="3">
+        <f>IF('Heure par heure'!D80="","",'Heure par heure'!D80-N('Heure par heure'!D79))</f>
+        <v/>
+      </c>
+      <c r="D80" s="3">
+        <f>IF('Heure par heure'!E80="","",'Heure par heure'!E80-N('Heure par heure'!E79))</f>
+        <v/>
+      </c>
+      <c r="E80" s="3">
+        <f>IF('Heure par heure'!F80="","",'Heure par heure'!F80-N('Heure par heure'!F79))</f>
+        <v/>
+      </c>
+      <c r="F80" s="3">
+        <f>SUM(B80:E80)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$6</f>
+              <f>'Jour par jour'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -908,12 +908,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2:$A$4</f>
+              <f>'Stories'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2:$B$4</f>
+              <f>'Stories'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1010,12 +1010,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$6</f>
+              <f>'Jour par jour'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1037,12 +1037,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$6</f>
+              <f>'Jour par jour'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$6</f>
+              <f>'Jour par jour'!$F$2:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1190,12 +1190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$6</f>
+              <f>'Jour par jour'!$H$2:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1292,12 +1292,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$6</f>
+              <f>'Jour par jour'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1394,12 +1394,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2:$D$4</f>
+              <f>'Vidéos'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1496,12 +1496,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2:$F$4</f>
+              <f>'Vidéos'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1523,12 +1523,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2:$G$4</f>
+              <f>'Vidéos'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1550,12 +1550,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2:$H$4</f>
+              <f>'Vidéos'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1577,12 +1577,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2:$I$4</f>
+              <f>'Vidéos'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1679,12 +1679,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2:$B$4</f>
+              <f>'Vidéos'!$B$2:$B$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2:$K$4</f>
+              <f>'Vidéos'!$K$2:$K$5</f>
             </numRef>
           </val>
         </ser>
@@ -1785,12 +1785,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$6</f>
+              <f>'Évolution par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1817,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$6</f>
+              <f>'Évolution par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1849,12 +1849,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$6</f>
+              <f>'Évolution par vidéo'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1947,12 +1979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1971,12 +2003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1995,12 +2027,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -2142,7 +2198,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2164,7 +2220,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2186,7 +2242,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2213,7 +2269,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2240,7 +2296,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2675,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2985,6 +3041,51 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <f>IF(ROW()=2,"",B7-B6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="E7" s="3">
+        <f>IF(ROW()=2,D7,D7-D6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2997,7 +3098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3214,14 +3315,61 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:54</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le budget 2026 de l'État affiche environ 135 </t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f>IFERROR((F5+G5+H5+I5)/IF(E5&gt;0,E5,D5),0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="6">
+        <f>IFERROR(D5/E5,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -3231,13 +3379,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3261,6 +3410,11 @@
           <t>Ton salaire brut n'est jamai</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Le budget 2026 de l'État aff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3273,6 +3427,7 @@
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3285,6 +3440,7 @@
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3301,6 +3457,7 @@
       <c r="D4" s="3" t="n">
         <v>68</v>
       </c>
+      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3317,6 +3474,7 @@
       <c r="D5" s="3" t="n">
         <v>94</v>
       </c>
+      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3332,6 +3490,26 @@
       </c>
       <c r="D6" s="3" t="n">
         <v>94</v>
+      </c>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3346,14 +3524,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3379,6 +3558,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Le budget 2026 de l'État aff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -3402,7 +3586,11 @@
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>SUM(B2:D2)</f>
+        <f>IF('Évolution par vidéo'!E2="","",'Évolution par vidéo'!E2)</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>SUM(B2:E2)</f>
         <v/>
       </c>
     </row>
@@ -3425,7 +3613,11 @@
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>SUM(B3:D3)</f>
+        <f>IF('Évolution par vidéo'!E3="","",'Évolution par vidéo'!E3-N('Évolution par vidéo'!E2))</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>SUM(B3:E3)</f>
         <v/>
       </c>
     </row>
@@ -3448,7 +3640,11 @@
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>SUM(B4:D4)</f>
+        <f>IF('Évolution par vidéo'!E4="","",'Évolution par vidéo'!E4-N('Évolution par vidéo'!E3))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>SUM(B4:E4)</f>
         <v/>
       </c>
     </row>
@@ -3471,7 +3667,11 @@
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>SUM(B5:D5)</f>
+        <f>IF('Évolution par vidéo'!E5="","",'Évolution par vidéo'!E5-N('Évolution par vidéo'!E4))</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>SUM(B5:E5)</f>
         <v/>
       </c>
     </row>
@@ -3494,7 +3694,38 @@
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>SUM(B6:D6)</f>
+        <f>IF('Évolution par vidéo'!E6="","",'Évolution par vidéo'!E6-N('Évolution par vidéo'!E5))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>SUM(B6:E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Évolution par vidéo'!B7="","",'Évolution par vidéo'!B7-N('Évolution par vidéo'!B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>IF('Évolution par vidéo'!C7="","",'Évolution par vidéo'!C7-N('Évolution par vidéo'!C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>IF('Évolution par vidéo'!D7="","",'Évolution par vidéo'!D7-N('Évolution par vidéo'!D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>IF('Évolution par vidéo'!E7="","",'Évolution par vidéo'!E7-N('Évolution par vidéo'!E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>SUM(B7:E7)</f>
         <v/>
       </c>
     </row>
@@ -7452,7 +7683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7612,14 +7843,82 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:38</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:55</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$80</f>
+              <f>'Heure par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$80</f>
+              <f>'Heure par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$80</f>
+              <f>'Heure par heure'!$E$2:$E$81</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$80</f>
+              <f>'Heure par heure'!$F$2:$F$81</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$80</f>
+              <f>'Heure par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$80</f>
+              <f>'Heure par heure'!$G$2:$G$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$80</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$81</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5574,6 +5574,32 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:00</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="G81" s="3">
+        <f>SUM(C81:F81)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5586,7 +5612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7668,6 +7694,32 @@
       </c>
       <c r="F80" s="3">
         <f>SUM(B80:E80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <f>'Heure par heure'!A81</f>
+        <v/>
+      </c>
+      <c r="B81" s="3">
+        <f>IF('Heure par heure'!C81="","",'Heure par heure'!C81-N('Heure par heure'!C80))</f>
+        <v/>
+      </c>
+      <c r="C81" s="3">
+        <f>IF('Heure par heure'!D81="","",'Heure par heure'!D81-N('Heure par heure'!D80))</f>
+        <v/>
+      </c>
+      <c r="D81" s="3">
+        <f>IF('Heure par heure'!E81="","",'Heure par heure'!E81-N('Heure par heure'!E80))</f>
+        <v/>
+      </c>
+      <c r="E81" s="3">
+        <f>IF('Heure par heure'!F81="","",'Heure par heure'!F81-N('Heure par heure'!F80))</f>
+        <v/>
+      </c>
+      <c r="F81" s="3">
+        <f>SUM(B81:E81)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$81</f>
+              <f>'Heure par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$81</f>
+              <f>'Heure par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$81</f>
+              <f>'Heure par heure'!$E$2:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$81</f>
+              <f>'Heure par heure'!$F$2:$F$82</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$81</f>
+              <f>'Heure par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$81</f>
+              <f>'Heure par heure'!$G$2:$G$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$81</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5600,6 +5600,32 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:00</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G82" s="3">
+        <f>SUM(C82:F82)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5612,7 +5638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7720,6 +7746,32 @@
       </c>
       <c r="F81" s="3">
         <f>SUM(B81:E81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <f>'Heure par heure'!A82</f>
+        <v/>
+      </c>
+      <c r="B82" s="3">
+        <f>IF('Heure par heure'!C82="","",'Heure par heure'!C82-N('Heure par heure'!C81))</f>
+        <v/>
+      </c>
+      <c r="C82" s="3">
+        <f>IF('Heure par heure'!D82="","",'Heure par heure'!D82-N('Heure par heure'!D81))</f>
+        <v/>
+      </c>
+      <c r="D82" s="3">
+        <f>IF('Heure par heure'!E82="","",'Heure par heure'!E82-N('Heure par heure'!E81))</f>
+        <v/>
+      </c>
+      <c r="E82" s="3">
+        <f>IF('Heure par heure'!F82="","",'Heure par heure'!F82-N('Heure par heure'!F81))</f>
+        <v/>
+      </c>
+      <c r="F82" s="3">
+        <f>SUM(B82:E82)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$82</f>
+              <f>'Heure par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$82</f>
+              <f>'Heure par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$82</f>
+              <f>'Heure par heure'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$82</f>
+              <f>'Heure par heure'!$F$2:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$82</f>
+              <f>'Heure par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$82</f>
+              <f>'Heure par heure'!$G$2:$G$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$82</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5626,6 +5626,32 @@
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="G83" s="3">
+        <f>SUM(C83:F83)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5638,7 +5664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7772,6 +7798,32 @@
       </c>
       <c r="F82" s="3">
         <f>SUM(B82:E82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <f>'Heure par heure'!A83</f>
+        <v/>
+      </c>
+      <c r="B83" s="3">
+        <f>IF('Heure par heure'!C83="","",'Heure par heure'!C83-N('Heure par heure'!C82))</f>
+        <v/>
+      </c>
+      <c r="C83" s="3">
+        <f>IF('Heure par heure'!D83="","",'Heure par heure'!D83-N('Heure par heure'!D82))</f>
+        <v/>
+      </c>
+      <c r="D83" s="3">
+        <f>IF('Heure par heure'!E83="","",'Heure par heure'!E83-N('Heure par heure'!E82))</f>
+        <v/>
+      </c>
+      <c r="E83" s="3">
+        <f>IF('Heure par heure'!F83="","",'Heure par heure'!F83-N('Heure par heure'!F82))</f>
+        <v/>
+      </c>
+      <c r="F83" s="3">
+        <f>SUM(B83:E83)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$83</f>
+              <f>'Heure par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$83</f>
+              <f>'Heure par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$83</f>
+              <f>'Heure par heure'!$E$2:$E$84</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$83</f>
+              <f>'Heure par heure'!$F$2:$F$84</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$83</f>
+              <f>'Heure par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$83</f>
+              <f>'Heure par heure'!$G$2:$G$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$83</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$84</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5652,6 +5652,32 @@
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:00</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G84" s="3">
+        <f>SUM(C84:F84)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5664,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7824,6 +7850,32 @@
       </c>
       <c r="F83" s="3">
         <f>SUM(B83:E83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <f>'Heure par heure'!A84</f>
+        <v/>
+      </c>
+      <c r="B84" s="3">
+        <f>IF('Heure par heure'!C84="","",'Heure par heure'!C84-N('Heure par heure'!C83))</f>
+        <v/>
+      </c>
+      <c r="C84" s="3">
+        <f>IF('Heure par heure'!D84="","",'Heure par heure'!D84-N('Heure par heure'!D83))</f>
+        <v/>
+      </c>
+      <c r="D84" s="3">
+        <f>IF('Heure par heure'!E84="","",'Heure par heure'!E84-N('Heure par heure'!E83))</f>
+        <v/>
+      </c>
+      <c r="E84" s="3">
+        <f>IF('Heure par heure'!F84="","",'Heure par heure'!F84-N('Heure par heure'!F83))</f>
+        <v/>
+      </c>
+      <c r="F84" s="3">
+        <f>SUM(B84:E84)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$84</f>
+              <f>'Heure par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$84</f>
+              <f>'Heure par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$84</f>
+              <f>'Heure par heure'!$E$2:$E$85</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$84</f>
+              <f>'Heure par heure'!$F$2:$F$85</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$84</f>
+              <f>'Heure par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$84</f>
+              <f>'Heure par heure'!$G$2:$G$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$84</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$85</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5678,6 +5678,32 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:00</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G85" s="3">
+        <f>SUM(C85:F85)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5690,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7876,6 +7902,32 @@
       </c>
       <c r="F84" s="3">
         <f>SUM(B84:E84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <f>'Heure par heure'!A85</f>
+        <v/>
+      </c>
+      <c r="B85" s="3">
+        <f>IF('Heure par heure'!C85="","",'Heure par heure'!C85-N('Heure par heure'!C84))</f>
+        <v/>
+      </c>
+      <c r="C85" s="3">
+        <f>IF('Heure par heure'!D85="","",'Heure par heure'!D85-N('Heure par heure'!D84))</f>
+        <v/>
+      </c>
+      <c r="D85" s="3">
+        <f>IF('Heure par heure'!E85="","",'Heure par heure'!E85-N('Heure par heure'!E84))</f>
+        <v/>
+      </c>
+      <c r="E85" s="3">
+        <f>IF('Heure par heure'!F85="","",'Heure par heure'!F85-N('Heure par heure'!F84))</f>
+        <v/>
+      </c>
+      <c r="F85" s="3">
+        <f>SUM(B85:E85)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -3055,17 +3055,17 @@
         <v/>
       </c>
       <c r="D7" s="3" t="n">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="E7" s="3">
         <f>IF(ROW()=2,D7,D7-D6)</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>94</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$85</f>
+              <f>'Heure par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$85</f>
+              <f>'Heure par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$85</f>
+              <f>'Heure par heure'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$85</f>
+              <f>'Heure par heure'!$F$2:$F$86</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$85</f>
+              <f>'Heure par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$85</f>
+              <f>'Heure par heure'!$G$2:$G$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$85</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5704,6 +5704,32 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:00</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G86" s="3">
+        <f>SUM(C86:F86)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5716,7 +5742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7928,6 +7954,32 @@
       </c>
       <c r="F85" s="3">
         <f>SUM(B85:E85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <f>'Heure par heure'!A86</f>
+        <v/>
+      </c>
+      <c r="B86" s="3">
+        <f>IF('Heure par heure'!C86="","",'Heure par heure'!C86-N('Heure par heure'!C85))</f>
+        <v/>
+      </c>
+      <c r="C86" s="3">
+        <f>IF('Heure par heure'!D86="","",'Heure par heure'!D86-N('Heure par heure'!D85))</f>
+        <v/>
+      </c>
+      <c r="D86" s="3">
+        <f>IF('Heure par heure'!E86="","",'Heure par heure'!E86-N('Heure par heure'!E85))</f>
+        <v/>
+      </c>
+      <c r="E86" s="3">
+        <f>IF('Heure par heure'!F86="","",'Heure par heure'!F86-N('Heure par heure'!F85))</f>
+        <v/>
+      </c>
+      <c r="F86" s="3">
+        <f>SUM(B86:E86)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$86</f>
+              <f>'Heure par heure'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$86</f>
+              <f>'Heure par heure'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$86</f>
+              <f>'Heure par heure'!$E$2:$E$87</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$86</f>
+              <f>'Heure par heure'!$F$2:$F$87</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$86</f>
+              <f>'Heure par heure'!$B$2:$B$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$86</f>
+              <f>'Heure par heure'!$G$2:$G$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$86</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$86</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$86</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$86</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$87</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5730,6 +5730,32 @@
         <v/>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:00</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G87" s="3">
+        <f>SUM(C87:F87)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5742,7 +5768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7980,6 +8006,32 @@
       </c>
       <c r="F86" s="3">
         <f>SUM(B86:E86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <f>'Heure par heure'!A87</f>
+        <v/>
+      </c>
+      <c r="B87" s="3">
+        <f>IF('Heure par heure'!C87="","",'Heure par heure'!C87-N('Heure par heure'!C86))</f>
+        <v/>
+      </c>
+      <c r="C87" s="3">
+        <f>IF('Heure par heure'!D87="","",'Heure par heure'!D87-N('Heure par heure'!D86))</f>
+        <v/>
+      </c>
+      <c r="D87" s="3">
+        <f>IF('Heure par heure'!E87="","",'Heure par heure'!E87-N('Heure par heure'!E86))</f>
+        <v/>
+      </c>
+      <c r="E87" s="3">
+        <f>IF('Heure par heure'!F87="","",'Heure par heure'!F87-N('Heure par heure'!F86))</f>
+        <v/>
+      </c>
+      <c r="F87" s="3">
+        <f>SUM(B87:E87)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$87</f>
+              <f>'Heure par heure'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$87</f>
+              <f>'Heure par heure'!$D$2:$D$88</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$87</f>
+              <f>'Heure par heure'!$E$2:$E$88</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$87</f>
+              <f>'Heure par heure'!$F$2:$F$88</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$87</f>
+              <f>'Heure par heure'!$B$2:$B$88</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$87</f>
+              <f>'Heure par heure'!$G$2:$G$88</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$87</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$87</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$87</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$88</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$87</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$88</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5756,6 +5756,32 @@
         <v/>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:00</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="G88" s="3">
+        <f>SUM(C88:F88)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5768,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8032,6 +8058,32 @@
       </c>
       <c r="F87" s="3">
         <f>SUM(B87:E87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <f>'Heure par heure'!A88</f>
+        <v/>
+      </c>
+      <c r="B88" s="3">
+        <f>IF('Heure par heure'!C88="","",'Heure par heure'!C88-N('Heure par heure'!C87))</f>
+        <v/>
+      </c>
+      <c r="C88" s="3">
+        <f>IF('Heure par heure'!D88="","",'Heure par heure'!D88-N('Heure par heure'!D87))</f>
+        <v/>
+      </c>
+      <c r="D88" s="3">
+        <f>IF('Heure par heure'!E88="","",'Heure par heure'!E88-N('Heure par heure'!E87))</f>
+        <v/>
+      </c>
+      <c r="E88" s="3">
+        <f>IF('Heure par heure'!F88="","",'Heure par heure'!F88-N('Heure par heure'!F87))</f>
+        <v/>
+      </c>
+      <c r="F88" s="3">
+        <f>SUM(B88:E88)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$88</f>
+              <f>'Heure par heure'!$C$2:$C$89</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$88</f>
+              <f>'Heure par heure'!$D$2:$D$89</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$88</f>
+              <f>'Heure par heure'!$E$2:$E$89</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$88</f>
+              <f>'Heure par heure'!$F$2:$F$89</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$88</f>
+              <f>'Heure par heure'!$B$2:$B$89</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$88</f>
+              <f>'Heure par heure'!$G$2:$G$89</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$88</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$89</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$88</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$89</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$88</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$89</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$88</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$89</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5782,6 +5782,32 @@
         <v/>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:00</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="G89" s="3">
+        <f>SUM(C89:F89)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5794,7 +5820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8084,6 +8110,32 @@
       </c>
       <c r="F88" s="3">
         <f>SUM(B88:E88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <f>'Heure par heure'!A89</f>
+        <v/>
+      </c>
+      <c r="B89" s="3">
+        <f>IF('Heure par heure'!C89="","",'Heure par heure'!C89-N('Heure par heure'!C88))</f>
+        <v/>
+      </c>
+      <c r="C89" s="3">
+        <f>IF('Heure par heure'!D89="","",'Heure par heure'!D89-N('Heure par heure'!D88))</f>
+        <v/>
+      </c>
+      <c r="D89" s="3">
+        <f>IF('Heure par heure'!E89="","",'Heure par heure'!E89-N('Heure par heure'!E88))</f>
+        <v/>
+      </c>
+      <c r="E89" s="3">
+        <f>IF('Heure par heure'!F89="","",'Heure par heure'!F89-N('Heure par heure'!F88))</f>
+        <v/>
+      </c>
+      <c r="F89" s="3">
+        <f>SUM(B89:E89)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$89</f>
+              <f>'Heure par heure'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$89</f>
+              <f>'Heure par heure'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$89</f>
+              <f>'Heure par heure'!$E$2:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$89</f>
+              <f>'Heure par heure'!$F$2:$F$90</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$89</f>
+              <f>'Heure par heure'!$B$2:$B$90</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$89</f>
+              <f>'Heure par heure'!$G$2:$G$90</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$89</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$89</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$89</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$89</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5808,6 +5808,32 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:00</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="G90" s="3">
+        <f>SUM(C90:F90)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5820,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8136,6 +8162,32 @@
       </c>
       <c r="F89" s="3">
         <f>SUM(B89:E89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <f>'Heure par heure'!A90</f>
+        <v/>
+      </c>
+      <c r="B90" s="3">
+        <f>IF('Heure par heure'!C90="","",'Heure par heure'!C90-N('Heure par heure'!C89))</f>
+        <v/>
+      </c>
+      <c r="C90" s="3">
+        <f>IF('Heure par heure'!D90="","",'Heure par heure'!D90-N('Heure par heure'!D89))</f>
+        <v/>
+      </c>
+      <c r="D90" s="3">
+        <f>IF('Heure par heure'!E90="","",'Heure par heure'!E90-N('Heure par heure'!E89))</f>
+        <v/>
+      </c>
+      <c r="E90" s="3">
+        <f>IF('Heure par heure'!F90="","",'Heure par heure'!F90-N('Heure par heure'!F89))</f>
+        <v/>
+      </c>
+      <c r="F90" s="3">
+        <f>SUM(B90:E90)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$90</f>
+              <f>'Heure par heure'!$C$2:$C$91</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$90</f>
+              <f>'Heure par heure'!$D$2:$D$91</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$90</f>
+              <f>'Heure par heure'!$E$2:$E$91</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$90</f>
+              <f>'Heure par heure'!$F$2:$F$91</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$90</f>
+              <f>'Heure par heure'!$B$2:$B$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$90</f>
+              <f>'Heure par heure'!$G$2:$G$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$90</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$91</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$90</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$91</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$90</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$91</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$90</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$91</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5834,6 +5834,32 @@
         <v/>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 19:00</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="G91" s="3">
+        <f>SUM(C91:F91)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5846,7 +5872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8188,6 +8214,32 @@
       </c>
       <c r="F90" s="3">
         <f>SUM(B90:E90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <f>'Heure par heure'!A91</f>
+        <v/>
+      </c>
+      <c r="B91" s="3">
+        <f>IF('Heure par heure'!C91="","",'Heure par heure'!C91-N('Heure par heure'!C90))</f>
+        <v/>
+      </c>
+      <c r="C91" s="3">
+        <f>IF('Heure par heure'!D91="","",'Heure par heure'!D91-N('Heure par heure'!D90))</f>
+        <v/>
+      </c>
+      <c r="D91" s="3">
+        <f>IF('Heure par heure'!E91="","",'Heure par heure'!E91-N('Heure par heure'!E90))</f>
+        <v/>
+      </c>
+      <c r="E91" s="3">
+        <f>IF('Heure par heure'!F91="","",'Heure par heure'!F91-N('Heure par heure'!F90))</f>
+        <v/>
+      </c>
+      <c r="F91" s="3">
+        <f>SUM(B91:E91)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$91</f>
+              <f>'Heure par heure'!$C$2:$C$92</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$91</f>
+              <f>'Heure par heure'!$D$2:$D$92</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$91</f>
+              <f>'Heure par heure'!$E$2:$E$92</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$91</f>
+              <f>'Heure par heure'!$F$2:$F$92</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$91</f>
+              <f>'Heure par heure'!$B$2:$B$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$91</f>
+              <f>'Heure par heure'!$G$2:$G$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$91</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$92</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$91</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$92</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$91</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$92</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$91</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$92</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5860,6 +5860,32 @@
         <v/>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 20:00</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G92" s="3">
+        <f>SUM(C92:F92)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5872,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8240,6 +8266,32 @@
       </c>
       <c r="F91" s="3">
         <f>SUM(B91:E91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <f>'Heure par heure'!A92</f>
+        <v/>
+      </c>
+      <c r="B92" s="3">
+        <f>IF('Heure par heure'!C92="","",'Heure par heure'!C92-N('Heure par heure'!C91))</f>
+        <v/>
+      </c>
+      <c r="C92" s="3">
+        <f>IF('Heure par heure'!D92="","",'Heure par heure'!D92-N('Heure par heure'!D91))</f>
+        <v/>
+      </c>
+      <c r="D92" s="3">
+        <f>IF('Heure par heure'!E92="","",'Heure par heure'!E92-N('Heure par heure'!E91))</f>
+        <v/>
+      </c>
+      <c r="E92" s="3">
+        <f>IF('Heure par heure'!F92="","",'Heure par heure'!F92-N('Heure par heure'!F91))</f>
+        <v/>
+      </c>
+      <c r="F92" s="3">
+        <f>SUM(B92:E92)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$92</f>
+              <f>'Heure par heure'!$C$2:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$92</f>
+              <f>'Heure par heure'!$D$2:$D$93</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$92</f>
+              <f>'Heure par heure'!$E$2:$E$93</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$92</f>
+              <f>'Heure par heure'!$F$2:$F$93</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$92</f>
+              <f>'Heure par heure'!$B$2:$B$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$92</f>
+              <f>'Heure par heure'!$G$2:$G$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$92</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$93</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$92</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$92</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$93</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$92</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$93</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5886,6 +5886,32 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G93" s="3">
+        <f>SUM(C93:F93)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5898,7 +5924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8292,6 +8318,32 @@
       </c>
       <c r="F92" s="3">
         <f>SUM(B92:E92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <f>'Heure par heure'!A93</f>
+        <v/>
+      </c>
+      <c r="B93" s="3">
+        <f>IF('Heure par heure'!C93="","",'Heure par heure'!C93-N('Heure par heure'!C92))</f>
+        <v/>
+      </c>
+      <c r="C93" s="3">
+        <f>IF('Heure par heure'!D93="","",'Heure par heure'!D93-N('Heure par heure'!D92))</f>
+        <v/>
+      </c>
+      <c r="D93" s="3">
+        <f>IF('Heure par heure'!E93="","",'Heure par heure'!E93-N('Heure par heure'!E92))</f>
+        <v/>
+      </c>
+      <c r="E93" s="3">
+        <f>IF('Heure par heure'!F93="","",'Heure par heure'!F93-N('Heure par heure'!F92))</f>
+        <v/>
+      </c>
+      <c r="F93" s="3">
+        <f>SUM(B93:E93)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$93</f>
+              <f>'Heure par heure'!$C$2:$C$94</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$93</f>
+              <f>'Heure par heure'!$D$2:$D$94</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$93</f>
+              <f>'Heure par heure'!$E$2:$E$94</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$93</f>
+              <f>'Heure par heure'!$F$2:$F$94</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$93</f>
+              <f>'Heure par heure'!$B$2:$B$94</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$93</f>
+              <f>'Heure par heure'!$G$2:$G$94</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$93</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$94</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$93</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$94</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$93</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$94</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$93</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$94</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5912,6 +5912,32 @@
         <v/>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:00</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="G94" s="3">
+        <f>SUM(C94:F94)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5924,7 +5950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8344,6 +8370,32 @@
       </c>
       <c r="F93" s="3">
         <f>SUM(B93:E93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <f>'Heure par heure'!A94</f>
+        <v/>
+      </c>
+      <c r="B94" s="3">
+        <f>IF('Heure par heure'!C94="","",'Heure par heure'!C94-N('Heure par heure'!C93))</f>
+        <v/>
+      </c>
+      <c r="C94" s="3">
+        <f>IF('Heure par heure'!D94="","",'Heure par heure'!D94-N('Heure par heure'!D93))</f>
+        <v/>
+      </c>
+      <c r="D94" s="3">
+        <f>IF('Heure par heure'!E94="","",'Heure par heure'!E94-N('Heure par heure'!E93))</f>
+        <v/>
+      </c>
+      <c r="E94" s="3">
+        <f>IF('Heure par heure'!F94="","",'Heure par heure'!F94-N('Heure par heure'!F93))</f>
+        <v/>
+      </c>
+      <c r="F94" s="3">
+        <f>SUM(B94:E94)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$94</f>
+              <f>'Heure par heure'!$C$2:$C$95</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$94</f>
+              <f>'Heure par heure'!$D$2:$D$95</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$94</f>
+              <f>'Heure par heure'!$E$2:$E$95</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$94</f>
+              <f>'Heure par heure'!$F$2:$F$95</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$94</f>
+              <f>'Heure par heure'!$B$2:$B$95</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$94</f>
+              <f>'Heure par heure'!$G$2:$G$95</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$94</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$95</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$94</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$95</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$94</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$95</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$94</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$95</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5938,6 +5938,32 @@
         <v/>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:00</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="G95" s="3">
+        <f>SUM(C95:F95)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5950,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8396,6 +8422,32 @@
       </c>
       <c r="F94" s="3">
         <f>SUM(B94:E94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <f>'Heure par heure'!A95</f>
+        <v/>
+      </c>
+      <c r="B95" s="3">
+        <f>IF('Heure par heure'!C95="","",'Heure par heure'!C95-N('Heure par heure'!C94))</f>
+        <v/>
+      </c>
+      <c r="C95" s="3">
+        <f>IF('Heure par heure'!D95="","",'Heure par heure'!D95-N('Heure par heure'!D94))</f>
+        <v/>
+      </c>
+      <c r="D95" s="3">
+        <f>IF('Heure par heure'!E95="","",'Heure par heure'!E95-N('Heure par heure'!E94))</f>
+        <v/>
+      </c>
+      <c r="E95" s="3">
+        <f>IF('Heure par heure'!F95="","",'Heure par heure'!F95-N('Heure par heure'!F94))</f>
+        <v/>
+      </c>
+      <c r="F95" s="3">
+        <f>SUM(B95:E95)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$95</f>
+              <f>'Heure par heure'!$C$2:$C$96</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$95</f>
+              <f>'Heure par heure'!$D$2:$D$96</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$95</f>
+              <f>'Heure par heure'!$E$2:$E$96</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$95</f>
+              <f>'Heure par heure'!$F$2:$F$96</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$95</f>
+              <f>'Heure par heure'!$B$2:$B$96</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$95</f>
+              <f>'Heure par heure'!$G$2:$G$96</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$95</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$96</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$95</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$96</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$95</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$96</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$95</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$96</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5964,6 +5964,32 @@
         <v/>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 06:00</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="G96" s="3">
+        <f>SUM(C96:F96)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5976,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8448,6 +8474,32 @@
       </c>
       <c r="F95" s="3">
         <f>SUM(B95:E95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <f>'Heure par heure'!A96</f>
+        <v/>
+      </c>
+      <c r="B96" s="3">
+        <f>IF('Heure par heure'!C96="","",'Heure par heure'!C96-N('Heure par heure'!C95))</f>
+        <v/>
+      </c>
+      <c r="C96" s="3">
+        <f>IF('Heure par heure'!D96="","",'Heure par heure'!D96-N('Heure par heure'!D95))</f>
+        <v/>
+      </c>
+      <c r="D96" s="3">
+        <f>IF('Heure par heure'!E96="","",'Heure par heure'!E96-N('Heure par heure'!E95))</f>
+        <v/>
+      </c>
+      <c r="E96" s="3">
+        <f>IF('Heure par heure'!F96="","",'Heure par heure'!F96-N('Heure par heure'!F95))</f>
+        <v/>
+      </c>
+      <c r="F96" s="3">
+        <f>SUM(B96:E96)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$96</f>
+              <f>'Heure par heure'!$C$2:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$96</f>
+              <f>'Heure par heure'!$D$2:$D$97</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$96</f>
+              <f>'Heure par heure'!$E$2:$E$97</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$96</f>
+              <f>'Heure par heure'!$F$2:$F$97</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$96</f>
+              <f>'Heure par heure'!$B$2:$B$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$96</f>
+              <f>'Heure par heure'!$G$2:$G$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$96</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$97</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$96</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$96</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$97</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$96</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$97</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5990,6 +5990,32 @@
         <v/>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:00</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="G97" s="3">
+        <f>SUM(C97:F97)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6002,7 +6028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8500,6 +8526,32 @@
       </c>
       <c r="F96" s="3">
         <f>SUM(B96:E96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <f>'Heure par heure'!A97</f>
+        <v/>
+      </c>
+      <c r="B97" s="3">
+        <f>IF('Heure par heure'!C97="","",'Heure par heure'!C97-N('Heure par heure'!C96))</f>
+        <v/>
+      </c>
+      <c r="C97" s="3">
+        <f>IF('Heure par heure'!D97="","",'Heure par heure'!D97-N('Heure par heure'!D96))</f>
+        <v/>
+      </c>
+      <c r="D97" s="3">
+        <f>IF('Heure par heure'!E97="","",'Heure par heure'!E97-N('Heure par heure'!E96))</f>
+        <v/>
+      </c>
+      <c r="E97" s="3">
+        <f>IF('Heure par heure'!F97="","",'Heure par heure'!F97-N('Heure par heure'!F96))</f>
+        <v/>
+      </c>
+      <c r="F97" s="3">
+        <f>SUM(B97:E97)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$97</f>
+              <f>'Heure par heure'!$C$2:$C$98</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$97</f>
+              <f>'Heure par heure'!$D$2:$D$98</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$97</f>
+              <f>'Heure par heure'!$E$2:$E$98</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$97</f>
+              <f>'Heure par heure'!$F$2:$F$98</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$97</f>
+              <f>'Heure par heure'!$B$2:$B$98</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$97</f>
+              <f>'Heure par heure'!$G$2:$G$98</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$97</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$98</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$97</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$98</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$97</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$98</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$97</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$98</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3741,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6016,6 +6016,32 @@
         <v/>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 08:00</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G98" s="3">
+        <f>SUM(C98:F98)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6028,7 +6054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8552,6 +8578,32 @@
       </c>
       <c r="F97" s="3">
         <f>SUM(B97:E97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <f>'Heure par heure'!A98</f>
+        <v/>
+      </c>
+      <c r="B98" s="3">
+        <f>IF('Heure par heure'!C98="","",'Heure par heure'!C98-N('Heure par heure'!C97))</f>
+        <v/>
+      </c>
+      <c r="C98" s="3">
+        <f>IF('Heure par heure'!D98="","",'Heure par heure'!D98-N('Heure par heure'!D97))</f>
+        <v/>
+      </c>
+      <c r="D98" s="3">
+        <f>IF('Heure par heure'!E98="","",'Heure par heure'!E98-N('Heure par heure'!E97))</f>
+        <v/>
+      </c>
+      <c r="E98" s="3">
+        <f>IF('Heure par heure'!F98="","",'Heure par heure'!F98-N('Heure par heure'!F97))</f>
+        <v/>
+      </c>
+      <c r="F98" s="3">
+        <f>SUM(B98:E98)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$7</f>
+              <f>'Jour par jour'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1010,12 +1010,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$7</f>
+              <f>'Jour par jour'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1037,12 +1037,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$7</f>
+              <f>'Jour par jour'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -1150,12 +1150,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$7</f>
+              <f>'Jour par jour'!$F$2:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1190,12 +1190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$7</f>
+              <f>'Jour par jour'!$H$2:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1292,12 +1292,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$7</f>
+              <f>'Jour par jour'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1785,12 +1785,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$7</f>
+              <f>'Évolution par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1817,12 +1817,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$7</f>
+              <f>'Évolution par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1849,12 +1849,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$7</f>
+              <f>'Évolution par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1881,12 +1881,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$E$2:$E$7</f>
+              <f>'Évolution par vidéo'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1979,12 +1979,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -2003,12 +2003,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -2027,12 +2027,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -2051,12 +2051,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$E$2:$E$7</f>
+              <f>'Vues du jour par vidéo'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -2269,7 +2269,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2296,7 +2296,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2731,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3084,6 +3084,51 @@
       </c>
       <c r="M7" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(ROW()=2,"",B8-B7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>543</v>
+      </c>
+      <c r="E8" s="3">
+        <f>IF(ROW()=2,D8,D8-D7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3332,10 +3377,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3379,7 +3424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3510,6 +3555,25 @@
       </c>
       <c r="E7" s="3" t="n">
         <v>106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3726,6 +3790,33 @@
       </c>
       <c r="F7" s="3">
         <f>SUM(B7:E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Évolution par vidéo'!B8="","",'Évolution par vidéo'!B8-N('Évolution par vidéo'!B7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF('Évolution par vidéo'!C8="","",'Évolution par vidéo'!C8-N('Évolution par vidéo'!C7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF('Évolution par vidéo'!D8="","",'Évolution par vidéo'!D8-N('Évolution par vidéo'!D7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>IF('Évolution par vidéo'!E8="","",'Évolution par vidéo'!E8-N('Évolution par vidéo'!E7))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>SUM(B8:E8)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$98</f>
+              <f>'Heure par heure'!$C$2:$C$99</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$98</f>
+              <f>'Heure par heure'!$D$2:$D$99</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$98</f>
+              <f>'Heure par heure'!$E$2:$E$99</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$98</f>
+              <f>'Heure par heure'!$F$2:$F$99</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$98</f>
+              <f>'Heure par heure'!$B$2:$B$99</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$98</f>
+              <f>'Heure par heure'!$G$2:$G$99</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$98</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$99</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$98</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$99</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$98</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$99</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$98</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$99</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6133,6 +6133,32 @@
         <v/>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 09:00</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G99" s="3">
+        <f>SUM(C99:F99)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6145,7 +6171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8695,6 +8721,32 @@
       </c>
       <c r="F98" s="3">
         <f>SUM(B98:E98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <f>'Heure par heure'!A99</f>
+        <v/>
+      </c>
+      <c r="B99" s="3">
+        <f>IF('Heure par heure'!C99="","",'Heure par heure'!C99-N('Heure par heure'!C98))</f>
+        <v/>
+      </c>
+      <c r="C99" s="3">
+        <f>IF('Heure par heure'!D99="","",'Heure par heure'!D99-N('Heure par heure'!D98))</f>
+        <v/>
+      </c>
+      <c r="D99" s="3">
+        <f>IF('Heure par heure'!E99="","",'Heure par heure'!E99-N('Heure par heure'!E98))</f>
+        <v/>
+      </c>
+      <c r="E99" s="3">
+        <f>IF('Heure par heure'!F99="","",'Heure par heure'!F99-N('Heure par heure'!F98))</f>
+        <v/>
+      </c>
+      <c r="F99" s="3">
+        <f>SUM(B99:E99)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$99</f>
+              <f>'Heure par heure'!$C$2:$C$100</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$99</f>
+              <f>'Heure par heure'!$D$2:$D$100</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$99</f>
+              <f>'Heure par heure'!$E$2:$E$100</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$99</f>
+              <f>'Heure par heure'!$F$2:$F$100</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$99</f>
+              <f>'Heure par heure'!$B$2:$B$100</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$99</f>
+              <f>'Heure par heure'!$G$2:$G$100</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$99</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$100</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$99</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$100</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$99</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$100</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$99</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$100</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6159,6 +6159,32 @@
         <v/>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:00</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G100" s="3">
+        <f>SUM(C100:F100)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6171,7 +6197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8747,6 +8773,32 @@
       </c>
       <c r="F99" s="3">
         <f>SUM(B99:E99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <f>'Heure par heure'!A100</f>
+        <v/>
+      </c>
+      <c r="B100" s="3">
+        <f>IF('Heure par heure'!C100="","",'Heure par heure'!C100-N('Heure par heure'!C99))</f>
+        <v/>
+      </c>
+      <c r="C100" s="3">
+        <f>IF('Heure par heure'!D100="","",'Heure par heure'!D100-N('Heure par heure'!D99))</f>
+        <v/>
+      </c>
+      <c r="D100" s="3">
+        <f>IF('Heure par heure'!E100="","",'Heure par heure'!E100-N('Heure par heure'!E99))</f>
+        <v/>
+      </c>
+      <c r="E100" s="3">
+        <f>IF('Heure par heure'!F100="","",'Heure par heure'!F100-N('Heure par heure'!F99))</f>
+        <v/>
+      </c>
+      <c r="F100" s="3">
+        <f>SUM(B100:E100)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$100</f>
+              <f>'Heure par heure'!$C$2:$C$101</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$100</f>
+              <f>'Heure par heure'!$D$2:$D$101</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$100</f>
+              <f>'Heure par heure'!$E$2:$E$101</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$100</f>
+              <f>'Heure par heure'!$F$2:$F$101</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$100</f>
+              <f>'Heure par heure'!$B$2:$B$101</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$100</f>
+              <f>'Heure par heure'!$G$2:$G$101</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$100</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$101</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$100</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$101</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$100</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$101</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$100</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$101</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6185,6 +6185,32 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 11:00</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G101" s="3">
+        <f>SUM(C101:F101)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6197,7 +6223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8799,6 +8825,32 @@
       </c>
       <c r="F100" s="3">
         <f>SUM(B100:E100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <f>'Heure par heure'!A101</f>
+        <v/>
+      </c>
+      <c r="B101" s="3">
+        <f>IF('Heure par heure'!C101="","",'Heure par heure'!C101-N('Heure par heure'!C100))</f>
+        <v/>
+      </c>
+      <c r="C101" s="3">
+        <f>IF('Heure par heure'!D101="","",'Heure par heure'!D101-N('Heure par heure'!D100))</f>
+        <v/>
+      </c>
+      <c r="D101" s="3">
+        <f>IF('Heure par heure'!E101="","",'Heure par heure'!E101-N('Heure par heure'!E100))</f>
+        <v/>
+      </c>
+      <c r="E101" s="3">
+        <f>IF('Heure par heure'!F101="","",'Heure par heure'!F101-N('Heure par heure'!F100))</f>
+        <v/>
+      </c>
+      <c r="F101" s="3">
+        <f>SUM(B101:E101)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$101</f>
+              <f>'Heure par heure'!$C$2:$C$102</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$101</f>
+              <f>'Heure par heure'!$D$2:$D$102</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$101</f>
+              <f>'Heure par heure'!$E$2:$E$102</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$101</f>
+              <f>'Heure par heure'!$F$2:$F$102</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$101</f>
+              <f>'Heure par heure'!$B$2:$B$102</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$101</f>
+              <f>'Heure par heure'!$G$2:$G$102</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$101</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$102</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$101</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$102</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$101</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$102</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$101</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$102</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6211,6 +6211,32 @@
         <v/>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 12:00</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G102" s="3">
+        <f>SUM(C102:F102)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6223,7 +6249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8851,6 +8877,32 @@
       </c>
       <c r="F101" s="3">
         <f>SUM(B101:E101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <f>'Heure par heure'!A102</f>
+        <v/>
+      </c>
+      <c r="B102" s="3">
+        <f>IF('Heure par heure'!C102="","",'Heure par heure'!C102-N('Heure par heure'!C101))</f>
+        <v/>
+      </c>
+      <c r="C102" s="3">
+        <f>IF('Heure par heure'!D102="","",'Heure par heure'!D102-N('Heure par heure'!D101))</f>
+        <v/>
+      </c>
+      <c r="D102" s="3">
+        <f>IF('Heure par heure'!E102="","",'Heure par heure'!E102-N('Heure par heure'!E101))</f>
+        <v/>
+      </c>
+      <c r="E102" s="3">
+        <f>IF('Heure par heure'!F102="","",'Heure par heure'!F102-N('Heure par heure'!F101))</f>
+        <v/>
+      </c>
+      <c r="F102" s="3">
+        <f>SUM(B102:E102)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_eco.xlsx
+++ b/suivi/Decode_suivi_eco.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$102</f>
+              <f>'Heure par heure'!$C$2:$C$103</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$102</f>
+              <f>'Heure par heure'!$D$2:$D$103</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$102</f>
+              <f>'Heure par heure'!$E$2:$E$103</f>
             </numRef>
           </val>
         </ser>
@@ -424,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$102</f>
+              <f>'Heure par heure'!$F$2:$F$103</f>
             </numRef>
           </val>
         </ser>
@@ -536,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$102</f>
+              <f>'Heure par heure'!$B$2:$B$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -649,12 +649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$G$2:$G$102</f>
+              <f>'Heure par heure'!$G$2:$G$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -748,12 +748,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$102</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$103</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$102</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$103</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +796,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$102</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$103</f>
             </numRef>
           </val>
         </ser>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$E$2:$E$102</f>
+              <f>'Vues gagnées par heure'!$E$2:$E$103</f>
             </numRef>
           </val>
         </ser>
@@ -2323,7 +2323,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2345,7 +2345,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2367,7 +2367,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2394,7 +2394,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3832,7 +3832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6237,6 +6237,32 @@
         <v/>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:00</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G103" s="3">
+        <f>SUM(C103:F103)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6249,7 +6275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8903,6 +8929,32 @@
       </c>
       <c r="F102" s="3">
         <f>SUM(B102:E102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <f>'Heure par heure'!A103</f>
+        <v/>
+      </c>
+      <c r="B103" s="3">
+        <f>IF('Heure par heure'!C103="","",'Heure par heure'!C103-N('Heure par heure'!C102))</f>
+        <v/>
+      </c>
+      <c r="C103" s="3">
+        <f>IF('Heure par heure'!D103="","",'Heure par heure'!D103-N('Heure par heure'!D102))</f>
+        <v/>
+      </c>
+      <c r="D103" s="3">
+        <f>IF('Heure par heure'!E103="","",'Heure par heure'!E103-N('Heure par heure'!E102))</f>
+        <v/>
+      </c>
+      <c r="E103" s="3">
+        <f>IF('Heure par heure'!F103="","",'Heure par heure'!F103-N('Heure par heure'!F102))</f>
+        <v/>
+      </c>
+      <c r="F103" s="3">
+        <f>SUM(B103:E103)</f>
         <v/>
       </c>
     </row>
